--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="583">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -940,6 +940,9 @@
     <t>1593: source value from V IMMUNIZATION - DATE/TIME RECORDED (#9000010.11-1205)</t>
   </si>
   <si>
+    <t>Immun.Immunization.RecordedDateTime</t>
+  </si>
+  <si>
     <t>Immunization.primarySource</t>
   </si>
   <si>
@@ -1360,7 +1363,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
 </t>
   </si>
   <si>
@@ -5853,15 +5856,15 @@
         <v>297</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5887,13 +5890,13 @@
         <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5943,7 +5946,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5961,30 +5964,30 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6010,13 +6013,13 @@
         <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6042,13 +6045,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -6066,7 +6069,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6084,13 +6087,13 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6104,10 +6107,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6130,13 +6133,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6187,7 +6190,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6202,16 +6205,16 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6225,10 +6228,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6251,13 +6254,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6308,7 +6311,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6326,19 +6329,19 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>80</v>
@@ -6346,10 +6349,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6375,10 +6378,10 @@
         <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6429,7 +6432,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6447,19 +6450,19 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>80</v>
@@ -6467,10 +6470,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6493,13 +6496,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6550,7 +6553,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6568,10 +6571,10 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6588,10 +6591,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6617,10 +6620,10 @@
         <v>168</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6647,13 +6650,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6671,7 +6674,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6689,16 +6692,16 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -6709,10 +6712,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6738,10 +6741,10 @@
         <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6768,13 +6771,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6792,7 +6795,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6810,16 +6813,16 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6830,10 +6833,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6856,13 +6859,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6913,7 +6916,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6931,10 +6934,10 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6943,18 +6946,18 @@
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7072,10 +7075,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7195,10 +7198,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7221,19 +7224,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7282,7 +7285,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7300,10 +7303,10 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -7312,18 +7315,18 @@
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7349,20 +7352,20 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>80</v>
@@ -7386,10 +7389,10 @@
         <v>160</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7410,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7425,10 +7428,10 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7445,10 +7448,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7474,14 +7477,14 @@
         <v>188</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7530,7 +7533,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7548,10 +7551,10 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7568,10 +7571,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7597,14 +7600,14 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7653,7 +7656,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7662,7 +7665,7 @@
         <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>103</v>
@@ -7671,10 +7674,10 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7691,10 +7694,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7720,16 +7723,16 @@
         <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7778,7 +7781,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7796,10 +7799,10 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7816,10 +7819,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7842,13 +7845,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7899,7 +7902,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7914,13 +7917,13 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7937,10 +7940,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8058,10 +8061,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8181,14 +8184,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8210,10 +8213,10 @@
         <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>140</v>
@@ -8268,7 +8271,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8306,10 +8309,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8335,10 +8338,10 @@
         <v>168</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8365,13 +8368,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8389,7 +8392,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8404,13 +8407,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8427,10 +8430,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8453,16 +8456,16 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8512,7 +8515,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>91</v>
@@ -8527,33 +8530,33 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8576,13 +8579,13 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8633,7 +8636,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8648,13 +8651,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8671,10 +8674,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8792,10 +8795,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8915,10 +8918,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8941,16 +8944,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9000,7 +9003,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9021,7 +9024,7 @@
         <v>134</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -9038,10 +9041,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9067,10 +9070,10 @@
         <v>289</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9121,7 +9124,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9142,7 +9145,7 @@
         <v>134</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9159,10 +9162,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9185,13 +9188,13 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9242,7 +9245,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>91</v>
@@ -9263,7 +9266,7 @@
         <v>134</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -9272,18 +9275,18 @@
         <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9309,10 +9312,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9339,13 +9342,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9363,7 +9366,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9378,13 +9381,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9401,10 +9404,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9427,13 +9430,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9484,7 +9487,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9499,7 +9502,7 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
@@ -9522,10 +9525,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9551,20 +9554,20 @@
         <v>241</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R61" t="s" s="2">
         <v>80</v>
@@ -9609,7 +9612,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9627,7 +9630,7 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>134</v>
@@ -9647,10 +9650,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9676,10 +9679,10 @@
         <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9706,13 +9709,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9730,7 +9733,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9768,10 +9771,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9794,13 +9797,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9851,7 +9854,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9863,7 +9866,7 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9889,10 +9892,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10010,10 +10013,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10133,14 +10136,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10162,10 +10165,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -10220,7 +10223,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10258,10 +10261,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10287,10 +10290,10 @@
         <v>188</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10341,7 +10344,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10359,7 +10362,7 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>134</v>
@@ -10379,10 +10382,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10408,10 +10411,10 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10462,7 +10465,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10500,10 +10503,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10529,10 +10532,10 @@
         <v>289</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10583,7 +10586,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10601,7 +10604,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>134</v>
@@ -10621,10 +10624,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10650,10 +10653,10 @@
         <v>289</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10704,7 +10707,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10722,7 +10725,7 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>134</v>
@@ -10742,10 +10745,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10771,10 +10774,10 @@
         <v>168</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10801,13 +10804,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10825,7 +10828,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10843,7 +10846,7 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>134</v>
@@ -10863,10 +10866,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10892,10 +10895,10 @@
         <v>168</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10922,13 +10925,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10946,7 +10949,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10984,10 +10987,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11010,16 +11013,16 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11069,7 +11072,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11087,10 +11090,10 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>80</v>
@@ -11107,10 +11110,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11228,10 +11231,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11351,14 +11354,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11380,10 +11383,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>140</v>
@@ -11438,7 +11441,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11476,10 +11479,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11505,10 +11508,10 @@
         <v>289</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11559,7 +11562,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11577,7 +11580,7 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>284</v>
@@ -11597,10 +11600,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11623,13 +11626,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11680,7 +11683,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11698,10 +11701,10 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
@@ -11710,7 +11713,7 @@
         <v>80</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>80</v>
@@ -11718,10 +11721,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11747,10 +11750,10 @@
         <v>241</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11801,7 +11804,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11819,10 +11822,10 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>80</v>
@@ -11839,10 +11842,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11865,13 +11868,13 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11922,7 +11925,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11960,10 +11963,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12081,10 +12084,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12204,14 +12207,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12233,10 +12236,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12291,7 +12294,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12329,10 +12332,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12358,10 +12361,10 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12412,7 +12415,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12450,10 +12453,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12476,13 +12479,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12533,7 +12536,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12571,10 +12574,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12600,10 +12603,10 @@
         <v>168</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12630,13 +12633,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -12654,7 +12657,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12692,10 +12695,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12718,16 +12721,16 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12775,7 +12778,7 @@
         <v>197</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>91</v>
@@ -12813,13 +12816,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>80</v>
@@ -12844,13 +12847,13 @@
         <v>188</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12900,7 +12903,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>91</v>
@@ -12930,18 +12933,18 @@
         <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12964,16 +12967,16 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13023,7 +13026,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$97</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="618">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,6 +968,114 @@
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
+</t>
+  </si>
+  <si>
+    <t>Mapping from permitted to transmitted</t>
+  </si>
+  <si>
+    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
+  </si>
+  <si>
+    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension.id</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension.extension</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.value[x]</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ConceptMap)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ConceptMap/CMVFimmunizationPrimarySource</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.value</t>
+  </si>
+  <si>
+    <t>Primitive value for boolean</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>boolean.value</t>
   </si>
   <si>
     <t>Immunization.reportOrigin</t>
@@ -2126,12 +2234,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ89"/>
+  <dimension ref="A1:AQ97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.78125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="80.68359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.7890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -6010,7 +6118,7 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>309</v>
@@ -6018,9 +6126,7 @@
       <c r="M32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>311</v>
-      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -6045,13 +6151,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -6069,7 +6175,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6081,19 +6187,19 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6107,10 +6213,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6121,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -6133,13 +6239,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>317</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6178,43 +6284,41 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6228,12 +6332,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
       </c>
@@ -6245,7 +6351,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
@@ -6254,15 +6360,17 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -6311,37 +6419,37 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>198</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>134</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>80</v>
@@ -6349,10 +6457,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6366,7 +6474,7 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
@@ -6378,10 +6486,10 @@
         <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>189</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6432,7 +6540,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6444,25 +6552,25 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>192</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>80</v>
@@ -6470,10 +6578,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6484,7 +6592,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6496,13 +6604,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>340</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6541,40 +6649,40 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>198</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6591,10 +6699,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6602,7 +6710,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>91</v>
@@ -6617,22 +6725,24 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6650,13 +6760,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>349</v>
+        <v>80</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6674,10 +6784,10 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>91</v>
@@ -6686,22 +6796,22 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>134</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -6712,10 +6822,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6723,7 +6833,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>91</v>
@@ -6738,13 +6848,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6756,7 +6866,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6771,13 +6881,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>357</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6795,7 +6905,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6813,16 +6923,16 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>134</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6833,10 +6943,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6850,7 +6960,7 @@
         <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
@@ -6859,13 +6969,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>362</v>
+        <v>241</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6916,7 +7026,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6928,16 +7038,16 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6946,18 +7056,18 @@
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6980,15 +7090,17 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>189</v>
+        <v>344</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -7013,13 +7125,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7037,7 +7149,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>191</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7049,19 +7161,19 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>192</v>
+        <v>350</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -7075,21 +7187,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -7101,17 +7213,15 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>352</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7148,43 +7258,43 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>198</v>
+        <v>351</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>192</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7198,10 +7308,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7221,23 +7331,19 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -7285,7 +7391,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7303,30 +7409,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7337,36 +7443,32 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>386</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7386,13 +7488,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -7410,7 +7512,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7428,19 +7530,19 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>80</v>
@@ -7448,10 +7550,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7471,21 +7573,19 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>188</v>
+        <v>375</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7533,7 +7633,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7551,10 +7651,10 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7571,10 +7671,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7594,21 +7694,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7632,13 +7730,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7656,7 +7754,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7665,7 +7763,7 @@
         <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>103</v>
@@ -7674,16 +7772,16 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7694,10 +7792,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7717,23 +7815,19 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7757,13 +7851,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>80</v>
+        <v>391</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7781,7 +7875,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7799,16 +7893,16 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7819,10 +7913,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7833,25 +7927,25 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7902,13 +7996,13 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
@@ -7917,13 +8011,13 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>417</v>
+        <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7932,18 +8026,18 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8061,10 +8155,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8134,16 +8228,16 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>198</v>
@@ -8184,45 +8278,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>146</v>
+        <v>411</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8271,28 +8365,28 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>134</v>
+        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8301,18 +8395,18 @@
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>80</v>
+        <v>416</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8323,32 +8417,36 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8368,13 +8466,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>430</v>
+        <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8392,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8407,13 +8505,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>425</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8430,10 +8528,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8441,13 +8539,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8456,18 +8554,18 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>436</v>
+        <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8515,10 +8613,10 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>91</v>
@@ -8530,33 +8628,33 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>443</v>
+        <v>80</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8567,7 +8665,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8579,16 +8677,18 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>446</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8636,28 +8736,28 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8674,10 +8774,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8697,19 +8797,23 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>189</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8757,7 +8861,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>191</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8769,16 +8873,16 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>192</v>
+        <v>447</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8795,14 +8899,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8818,20 +8922,18 @@
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>449</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>138</v>
+        <v>450</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8868,19 +8970,19 @@
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>198</v>
+        <v>448</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8892,16 +8994,16 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>452</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>192</v>
+        <v>454</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8918,10 +9020,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8941,20 +9043,18 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>455</v>
+        <v>188</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>456</v>
+        <v>189</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9003,7 +9103,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>191</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9015,16 +9115,16 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>460</v>
+        <v>192</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -9041,21 +9141,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -9064,18 +9164,20 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>289</v>
+        <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>138</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9124,28 +9226,28 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>464</v>
+        <v>198</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>465</v>
+        <v>192</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9162,42 +9264,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>467</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -9245,29 +9351,29 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>471</v>
-      </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
@@ -9275,18 +9381,18 @@
         <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9297,7 +9403,7 @@
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -9306,16 +9412,16 @@
         <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9342,13 +9448,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9366,13 +9472,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -9381,13 +9487,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9404,10 +9510,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9415,30 +9521,32 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9487,13 +9595,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9502,33 +9610,33 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>134</v>
+        <v>476</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>80</v>
+        <v>478</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>80</v>
+        <v>479</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9539,36 +9647,32 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>241</v>
+        <v>481</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9612,13 +9716,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -9627,13 +9731,13 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>134</v>
+        <v>486</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -9650,10 +9754,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9664,7 +9768,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9676,13 +9780,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>492</v>
+        <v>189</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>493</v>
+        <v>190</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9709,13 +9813,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>494</v>
+        <v>80</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9733,19 +9837,19 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>491</v>
+        <v>191</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9754,7 +9858,7 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>80</v>
@@ -9771,14 +9875,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9797,15 +9901,17 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>414</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9842,19 +9948,19 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>496</v>
+        <v>198</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9866,7 +9972,7 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>499</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9875,7 +9981,7 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
@@ -9892,10 +9998,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9915,18 +10021,20 @@
         <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>188</v>
+        <v>490</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>189</v>
+        <v>491</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9975,7 +10083,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>191</v>
+        <v>494</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9987,16 +10095,16 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>192</v>
+        <v>495</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -10013,21 +10121,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -10036,20 +10144,18 @@
         <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>137</v>
+        <v>289</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>138</v>
+        <v>497</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10098,28 +10204,28 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>198</v>
+        <v>499</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>192</v>
+        <v>500</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>80</v>
@@ -10136,46 +10242,42 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>137</v>
+        <v>502</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>424</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
       </c>
@@ -10223,28 +10325,28 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>426</v>
+        <v>505</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>134</v>
+        <v>506</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>80</v>
@@ -10253,18 +10355,18 @@
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>80</v>
+        <v>507</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>80</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10275,7 +10377,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -10287,13 +10389,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10320,13 +10422,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>80</v>
+        <v>512</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10344,13 +10446,13 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
@@ -10359,13 +10461,13 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>80</v>
+        <v>514</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>506</v>
+        <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>134</v>
+        <v>515</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
@@ -10382,10 +10484,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10396,7 +10498,7 @@
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>80</v>
@@ -10408,13 +10510,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>105</v>
+        <v>517</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10465,13 +10567,13 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
@@ -10480,7 +10582,7 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>80</v>
+        <v>519</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
@@ -10503,10 +10605,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10523,26 +10625,30 @@
         <v>80</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q69" s="2"/>
+      <c r="Q69" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
       </c>
@@ -10586,7 +10692,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10604,7 +10710,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>134</v>
@@ -10624,10 +10730,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10638,7 +10744,7 @@
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>80</v>
@@ -10650,13 +10756,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>289</v>
+        <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10683,13 +10789,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>80</v>
+        <v>529</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10707,13 +10813,13 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
@@ -10725,7 +10831,7 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>134</v>
@@ -10745,10 +10851,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10771,13 +10877,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>168</v>
+        <v>449</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10804,13 +10910,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10828,7 +10934,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10840,13 +10946,13 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>534</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>523</v>
+        <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>134</v>
@@ -10866,10 +10972,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10892,13 +10998,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>525</v>
+        <v>189</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>526</v>
+        <v>190</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10925,13 +11031,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10949,7 +11055,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>524</v>
+        <v>191</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10961,7 +11067,7 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -10970,7 +11076,7 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>80</v>
@@ -10987,14 +11093,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11013,16 +11119,16 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>414</v>
+        <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>530</v>
+        <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>531</v>
+        <v>194</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>532</v>
+        <v>140</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11072,7 +11178,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>529</v>
+        <v>198</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11084,16 +11190,16 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>533</v>
+        <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>534</v>
+        <v>192</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>80</v>
@@ -11110,42 +11216,46 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>189</v>
+        <v>459</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
       </c>
@@ -11193,19 +11303,19 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>191</v>
+        <v>461</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
@@ -11214,7 +11324,7 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>80</v>
@@ -11231,21 +11341,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>80</v>
@@ -11257,17 +11367,15 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>138</v>
+        <v>539</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11316,28 +11424,28 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>198</v>
+        <v>538</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>80</v>
+        <v>541</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>80</v>
@@ -11354,46 +11462,42 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>424</v>
+        <v>543</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11441,19 +11545,19 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>426</v>
+        <v>542</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
@@ -11479,10 +11583,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11508,10 +11612,10 @@
         <v>289</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11562,7 +11666,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11580,10 +11684,10 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>80</v>
@@ -11600,10 +11704,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11617,7 +11721,7 @@
         <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>80</v>
@@ -11626,13 +11730,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>543</v>
+        <v>289</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11683,7 +11787,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11701,10 +11805,10 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>547</v>
+        <v>134</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
@@ -11713,7 +11817,7 @@
         <v>80</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>548</v>
+        <v>80</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>80</v>
@@ -11721,10 +11825,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11735,7 +11839,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11747,13 +11851,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11780,13 +11884,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>80</v>
+        <v>556</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11804,13 +11908,13 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
@@ -11822,10 +11926,10 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>553</v>
+        <v>134</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>80</v>
@@ -11842,10 +11946,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11856,7 +11960,7 @@
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
@@ -11868,13 +11972,13 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>414</v>
+        <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11901,13 +12005,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>80</v>
+        <v>562</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>80</v>
+        <v>563</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -11925,13 +12029,13 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
@@ -11963,10 +12067,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11977,7 +12081,7 @@
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11989,15 +12093,17 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>188</v>
+        <v>449</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>189</v>
+        <v>565</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12046,28 +12152,28 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>191</v>
+        <v>564</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>80</v>
+        <v>568</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>192</v>
+        <v>569</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>80</v>
@@ -12084,21 +12190,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -12110,17 +12216,15 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12169,19 +12273,19 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -12207,14 +12311,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>423</v>
+        <v>136</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12227,26 +12331,24 @@
         <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>424</v>
+        <v>138</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>425</v>
+        <v>194</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -12294,7 +12396,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>426</v>
+        <v>198</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12315,7 +12417,7 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>80</v>
@@ -12332,42 +12434,46 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>561</v>
+        <v>459</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
       </c>
@@ -12415,19 +12521,19 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>560</v>
+        <v>461</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
@@ -12453,10 +12559,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12479,13 +12585,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12536,7 +12642,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12554,10 +12660,10 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>80</v>
+        <v>576</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>134</v>
+        <v>284</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
@@ -12574,10 +12680,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12588,10 +12694,10 @@
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>80</v>
@@ -12600,13 +12706,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>168</v>
+        <v>578</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12633,13 +12739,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>569</v>
+        <v>80</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -12657,13 +12763,13 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
@@ -12675,10 +12781,10 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>134</v>
+        <v>582</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
@@ -12687,7 +12793,7 @@
         <v>80</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>80</v>
+        <v>583</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>80</v>
@@ -12695,10 +12801,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12706,7 +12812,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>91</v>
@@ -12721,17 +12827,15 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>572</v>
+        <v>241</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12768,20 +12872,22 @@
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>91</v>
@@ -12796,10 +12902,10 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>80</v>
+        <v>587</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>134</v>
+        <v>588</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
@@ -12816,14 +12922,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>80</v>
       </c>
@@ -12832,10 +12936,10 @@
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12844,17 +12948,15 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>188</v>
+        <v>449</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12903,13 +13005,13 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
@@ -12933,18 +13035,18 @@
         <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>578</v>
+        <v>80</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>579</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12967,17 +13069,15 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>572</v>
+        <v>188</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>581</v>
+        <v>189</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13026,7 +13126,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>580</v>
+        <v>191</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13038,32 +13138,1012 @@
         <v>80</v>
       </c>
       <c r="AJ89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AN89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
+      <c r="AN92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AC95" s="2"/>
+      <c r="AD95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ89">
+  <autoFilter ref="A1:AQ97">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13073,7 +14153,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI96">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>299: transform using "not-done" on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
+    <t>299: transform using #not-done on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationNameIEN</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="619">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,7 +532,8 @@
     <t>299: transform using #not-done on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
-    <t>Immun.Immunization.ImmunizationNameIEN</t>
+    <t>Immun.Immunization.ImmunizationNameIEN
+Dim.ImmunizationName.ImmunizationName,Dim.PharmacyOrderableItem.ImmunizationName</t>
   </si>
   <si>
     <t>Immunization.statusReason</t>
@@ -595,6 +596,10 @@
   </si>
   <si>
     <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationNameIEN
+Dim.ImmunizationName.CVXCode</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.id</t>
@@ -2278,7 +2283,7 @@
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="158.05078125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="191.34765625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="53.78515625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="87.71484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3998,15 +4003,15 @@
         <v>186</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4029,13 +4034,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4086,7 +4091,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4107,7 +4112,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -4124,10 +4129,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4156,7 +4161,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -4197,19 +4202,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4230,7 +4235,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -4247,10 +4252,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4273,19 +4278,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4334,7 +4339,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4352,10 +4357,10 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -4372,10 +4377,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4398,13 +4403,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4455,7 +4460,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4476,7 +4481,7 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -4493,10 +4498,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4525,7 +4530,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4566,19 +4571,19 @@
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4599,7 +4604,7 @@
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -4616,10 +4621,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4645,16 +4650,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4703,7 +4708,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4721,10 +4726,10 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -4741,10 +4746,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4767,16 +4772,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4826,7 +4831,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4844,10 +4849,10 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
@@ -4864,10 +4869,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4893,14 +4898,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4949,7 +4954,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4967,10 +4972,10 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4979,7 +4984,7 @@
         <v>80</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -4987,10 +4992,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5013,17 +5018,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5072,7 +5077,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5090,10 +5095,10 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -5110,10 +5115,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5136,19 +5141,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5197,7 +5202,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5215,10 +5220,10 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
@@ -5235,10 +5240,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5261,19 +5266,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5322,7 +5327,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5340,10 +5345,10 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -5360,14 +5365,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5386,13 +5391,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5443,7 +5448,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5458,33 +5463,33 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5507,13 +5512,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5564,7 +5569,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5579,16 +5584,16 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -5602,10 +5607,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5628,16 +5633,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5675,17 +5680,17 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5700,19 +5705,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5723,13 +5728,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5751,16 +5756,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5810,7 +5815,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5825,33 +5830,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5874,13 +5879,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5931,7 +5936,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5952,27 +5957,27 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5995,16 +6000,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6054,7 +6059,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6072,30 +6077,30 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6118,13 +6123,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6175,7 +6180,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6213,10 +6218,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6242,10 +6247,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6284,17 +6289,17 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6332,13 +6337,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6360,16 +6365,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6419,7 +6424,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6428,7 +6433,7 @@
         <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>142</v>
@@ -6457,10 +6462,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6483,13 +6488,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6540,7 +6545,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6561,7 +6566,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6578,10 +6583,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6607,10 +6612,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6649,19 +6654,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6699,10 +6704,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6728,13 +6733,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6742,7 +6747,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6784,7 +6789,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6822,10 +6827,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6848,13 +6853,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6866,7 +6871,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6905,7 +6910,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6943,10 +6948,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6969,13 +6974,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7026,7 +7031,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7064,10 +7069,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7093,13 +7098,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7125,13 +7130,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7149,7 +7154,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7167,13 +7172,13 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -7187,10 +7192,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7213,13 +7218,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7270,7 +7275,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7285,16 +7290,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7308,10 +7313,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7334,13 +7339,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7391,7 +7396,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7409,19 +7414,19 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>80</v>
@@ -7429,10 +7434,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7455,13 +7460,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7512,7 +7517,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7530,19 +7535,19 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>80</v>
@@ -7550,10 +7555,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7576,13 +7581,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7633,7 +7638,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7651,10 +7656,10 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7671,10 +7676,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7700,10 +7705,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7730,13 +7735,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7754,7 +7759,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7772,16 +7777,16 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7792,10 +7797,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7821,10 +7826,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7851,13 +7856,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7875,7 +7880,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7893,16 +7898,16 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7913,10 +7918,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7939,13 +7944,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7996,7 +8001,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8014,10 +8019,10 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -8026,18 +8031,18 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8060,13 +8065,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8117,7 +8122,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8138,7 +8143,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -8155,10 +8160,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8187,7 +8192,7 @@
         <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -8228,19 +8233,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8261,7 +8266,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8278,10 +8283,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8304,19 +8309,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8365,7 +8370,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8383,10 +8388,10 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8395,18 +8400,18 @@
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8432,20 +8437,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8469,10 +8474,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8490,7 +8495,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8508,10 +8513,10 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8528,10 +8533,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8554,17 +8559,17 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8613,7 +8618,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8631,10 +8636,10 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8651,10 +8656,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8680,14 +8685,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8736,7 +8741,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8745,7 +8750,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8754,10 +8759,10 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8774,10 +8779,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8803,16 +8808,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8861,7 +8866,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8879,10 +8884,10 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8899,10 +8904,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8925,13 +8930,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8982,7 +8987,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8997,13 +9002,13 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -9020,10 +9025,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9046,13 +9051,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9103,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9124,7 +9129,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -9141,10 +9146,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9173,7 +9178,7 @@
         <v>138</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -9226,7 +9231,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9247,7 +9252,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9264,14 +9269,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9293,10 +9298,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9351,7 +9356,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9389,10 +9394,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9418,10 +9423,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9448,13 +9453,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9472,7 +9477,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9487,13 +9492,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9510,10 +9515,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9536,16 +9541,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9595,7 +9600,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9610,33 +9615,33 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9659,13 +9664,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9716,7 +9721,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9731,13 +9736,13 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -9754,10 +9759,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9780,13 +9785,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9837,7 +9842,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9858,7 +9863,7 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>80</v>
@@ -9875,10 +9880,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9907,7 +9912,7 @@
         <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -9948,19 +9953,19 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9981,7 +9986,7 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
@@ -9998,10 +10003,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10024,16 +10029,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10083,7 +10088,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10104,7 +10109,7 @@
         <v>134</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -10121,10 +10126,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10147,13 +10152,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10204,7 +10209,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10225,7 +10230,7 @@
         <v>134</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>80</v>
@@ -10242,10 +10247,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10268,13 +10273,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10325,7 +10330,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10346,7 +10351,7 @@
         <v>134</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>80</v>
@@ -10355,18 +10360,18 @@
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10392,10 +10397,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10422,13 +10427,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10446,7 +10451,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10461,13 +10466,13 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
@@ -10484,10 +10489,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10510,13 +10515,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10567,7 +10572,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10582,7 +10587,7 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
@@ -10605,10 +10610,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10631,23 +10636,23 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10692,7 +10697,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10710,7 +10715,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>134</v>
@@ -10730,10 +10735,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10759,10 +10764,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10789,13 +10794,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10813,7 +10818,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10851,10 +10856,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10877,13 +10882,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10934,7 +10939,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10946,7 +10951,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10972,10 +10977,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10998,13 +11003,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11055,7 +11060,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11076,7 +11081,7 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>80</v>
@@ -11093,10 +11098,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11125,7 +11130,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -11178,7 +11183,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11199,7 +11204,7 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>80</v>
@@ -11216,14 +11221,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11245,10 +11250,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11303,7 +11308,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11341,10 +11346,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11367,13 +11372,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11424,7 +11429,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11442,7 +11447,7 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>134</v>
@@ -11462,10 +11467,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11491,10 +11496,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11545,7 +11550,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11583,10 +11588,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11609,13 +11614,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11666,7 +11671,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11684,7 +11689,7 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>134</v>
@@ -11704,10 +11709,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11730,13 +11735,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11787,7 +11792,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11805,7 +11810,7 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>134</v>
@@ -11825,10 +11830,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11854,10 +11859,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11884,13 +11889,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11908,7 +11913,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11926,7 +11931,7 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>134</v>
@@ -11946,10 +11951,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11975,10 +11980,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12005,13 +12010,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12029,7 +12034,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12067,10 +12072,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12093,16 +12098,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12152,7 +12157,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12170,10 +12175,10 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>80</v>
@@ -12190,10 +12195,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12216,13 +12221,13 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12273,7 +12278,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12294,7 +12299,7 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>80</v>
@@ -12311,10 +12316,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12343,7 +12348,7 @@
         <v>138</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12396,7 +12401,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12417,7 +12422,7 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>80</v>
@@ -12434,14 +12439,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12463,10 +12468,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12521,7 +12526,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12559,10 +12564,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12585,13 +12590,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12642,7 +12647,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12660,10 +12665,10 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
@@ -12680,10 +12685,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12706,13 +12711,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12763,7 +12768,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12781,10 +12786,10 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
@@ -12793,7 +12798,7 @@
         <v>80</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>80</v>
@@ -12801,10 +12806,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12827,13 +12832,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12884,7 +12889,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12902,10 +12907,10 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
@@ -12922,10 +12927,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12948,13 +12953,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13005,7 +13010,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13043,10 +13048,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13069,13 +13074,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13126,7 +13131,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13147,7 +13152,7 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
@@ -13164,10 +13169,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13196,7 +13201,7 @@
         <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>140</v>
@@ -13249,7 +13254,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13270,7 +13275,7 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -13287,14 +13292,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13316,10 +13321,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13374,7 +13379,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13412,10 +13417,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13438,13 +13443,13 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13495,7 +13500,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13533,10 +13538,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13559,13 +13564,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13616,7 +13621,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13654,10 +13659,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13683,10 +13688,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13713,13 +13718,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13737,7 +13742,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13775,10 +13780,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13801,16 +13806,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13848,17 +13853,17 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13896,13 +13901,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13924,16 +13929,16 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13983,7 +13988,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14013,18 +14018,18 @@
         <v>80</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14047,16 +14052,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14106,7 +14111,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,12 +256,6 @@
   </si>
   <si>
     <t>Mapping: CDA (R2)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -520,15 +520,6 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
     <t>299: transform using #not-done on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
@@ -536,6 +527,15 @@
 Dim.ImmunizationName.ImmunizationName,Dim.PharmacyOrderableItem.ImmunizationName</t>
   </si>
   <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
     <t>Immunization.statusReason</t>
   </si>
   <si>
@@ -555,13 +555,13 @@
     <t>http://va.gov/fhir/ValueSet/VSVFimmunizationStatusReason</t>
   </si>
   <si>
+    <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
+  </si>
+  <si>
     <t>Event.statusReason</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN].reasonCOde</t>
-  </si>
-  <si>
-    <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
   </si>
   <si>
     <t>Immunization.vaccineCode</t>
@@ -580,21 +580,6 @@
 </t>
   </si>
   <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>RXA-5</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
-  </si>
-  <si>
     <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
   </si>
   <si>
@@ -602,6 +587,21 @@
 Dim.ImmunizationName.CVXCode</t>
   </si>
   <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>RXA-5</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
+  </si>
+  <si>
     <t>Immunization.vaccineCode.id</t>
   </si>
   <si>
@@ -734,13 +734,13 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>1609: source value from IMMUNIZATION LOT - NDC CODE (VA) (#9999999.41-.18)</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
     <t>./code</t>
-  </si>
-  <si>
-    <t>1609: source value from IMMUNIZATION LOT - NDC CODE (VA) (#9999999.41-.18)</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.display</t>
@@ -833,6 +833,12 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
+    <t>333: source value from V IMMUNIZATION - PATIENT NAME (#9000010.11-.02)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -843,12 +849,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>333: source value from V IMMUNIZATION - PATIENT NAME (#9000010.11-.02)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.PatientIEN</t>
   </si>
   <si>
     <t>Immunization.encounter</t>
@@ -936,18 +936,18 @@
     <t>The date the occurrence of the immunization was first captured in the record - potentially significantly after the occurrence of the event.</t>
   </si>
   <si>
+    <t>1593: source value from V IMMUNIZATION - DATE/TIME RECORDED (#9000010.11-1205)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.RecordedDateTime</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].time</t>
   </si>
   <si>
     <t>FiveWs.recorded</t>
   </si>
   <si>
-    <t>1593: source value from V IMMUNIZATION - DATE/TIME RECORDED (#9000010.11-1205)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.RecordedDateTime</t>
-  </si>
-  <si>
     <t>Immunization.primarySource</t>
   </si>
   <si>
@@ -960,6 +960,12 @@
     <t>Reflects the “reliability” of the content.</t>
   </si>
   <si>
+    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
+  </si>
+  <si>
     <t>RXA-9</t>
   </si>
   <si>
@@ -967,12 +973,6 @@
   </si>
   <si>
     <t>FiveWs.source</t>
-  </si>
-  <si>
-    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
   </si>
   <si>
     <t>Immunization.primarySource.id</t>
@@ -1145,6 +1145,9 @@
     <t>Name of vaccine manufacturer.</t>
   </si>
   <si>
+    <t>339: source value from IMMUNIZATION LOT - MANUFACTURER (#9999999.41-.02)</t>
+  </si>
+  <si>
     <t>RXA-17</t>
   </si>
   <si>
@@ -1154,9 +1157,6 @@
     <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacuturerOrganization/name</t>
   </si>
   <si>
-    <t>339: source value from IMMUNIZATION LOT - MANUFACTURER (#9999999.41-.02)</t>
-  </si>
-  <si>
     <t>Immunization.lotNumber</t>
   </si>
   <si>
@@ -1166,6 +1166,9 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
+    <t>338: source value from IMMUNIZATION LOT - LOT NUMBER (#9999999.41-.01)</t>
+  </si>
+  <si>
     <t>RXA-15</t>
   </si>
   <si>
@@ -1173,9 +1176,6 @@
   </si>
   <si>
     <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/lotNumberText</t>
-  </si>
-  <si>
-    <t>338: source value from IMMUNIZATION LOT - LOT NUMBER (#9999999.41-.01)</t>
   </si>
   <si>
     <t>Immunization.expirationDate</t>
@@ -1258,16 +1258,16 @@
     <t>The quantity of vaccine product that was administered.</t>
   </si>
   <si>
+    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (#9000010.11-1313 &gt; 757.5-)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.DoseUnit</t>
+  </si>
+  <si>
     <t>RXA-6 / RXA-7</t>
   </si>
   <si>
     <t>.doseQuantity</t>
-  </si>
-  <si>
-    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (#9000010.11-1313 &gt; 757.5-)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.DoseUnit</t>
   </si>
   <si>
     <t>Immunization.doseQuantity.id</t>
@@ -1298,16 +1298,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>340: source value from V IMMUNIZATION - DOSE (#9000010.11-1312)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.Dosage</t>
+  </si>
+  <si>
     <t>SN.2  / CQ - N/A</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>340: source value from V IMMUNIZATION - DOSE (#9000010.11-1312)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.Dosage</t>
   </si>
   <si>
     <t>Immunization.doseQuantity.comparator</t>
@@ -1489,6 +1489,12 @@
     <t>When the individual practitioner who performed the action is known, it is best to send.</t>
   </si>
   <si>
+    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (#9000010.11-1204)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizingStaffIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1496,12 +1502,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (#9000010.11-1204)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizingStaffIEN</t>
   </si>
   <si>
     <t>Immunization.note</t>
@@ -1585,13 +1585,13 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>343: source value from V IMMUNIZATION - COMMENTS (#9000010.11-81101)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationComments</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>343: source value from V IMMUNIZATION - COMMENTS (#9000010.11-81101)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizationComments</t>
   </si>
   <si>
     <t>Immunization.reasonCode</t>
@@ -1813,13 +1813,13 @@
     <t>Details of the reaction.</t>
   </si>
   <si>
+    <t>1673: reference</t>
+  </si>
+  <si>
     <t>OBX-5</t>
   </si>
   <si>
     <t>.value</t>
-  </si>
-  <si>
-    <t>1673: reference</t>
   </si>
   <si>
     <t>Immunization.reaction.reported</t>
@@ -2277,13 +2277,13 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="147.5546875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="236.8828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="158.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="191.34765625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="87.71484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="191.34765625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.71484375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="236.8828125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="158.05078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2519,19 +2519,19 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>80</v>
@@ -3138,13 +3138,13 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>80</v>
@@ -3261,13 +3261,13 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>80</v>
@@ -3384,13 +3384,13 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>80</v>
@@ -3509,13 +3509,13 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>80</v>
@@ -3624,25 +3624,25 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3748,22 +3748,22 @@
         <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" hidden="true">
@@ -3869,7 +3869,7 @@
         <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>174</v>
@@ -3878,13 +3878,13 @@
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -4112,13 +4112,13 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -4235,13 +4235,13 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -4357,16 +4357,16 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4481,13 +4481,13 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4604,13 +4604,13 @@
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4726,16 +4726,16 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4849,16 +4849,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4969,22 +4969,22 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AN22" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AO22" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -5095,16 +5095,16 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5220,16 +5220,16 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5345,16 +5345,16 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5475,13 +5475,13 @@
         <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5584,22 +5584,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5705,25 +5705,25 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5830,25 +5830,25 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5951,25 +5951,25 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -6074,25 +6074,25 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -6442,16 +6442,16 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -6566,13 +6566,13 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6810,13 +6810,13 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -6931,13 +6931,13 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -7172,19 +7172,19 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7290,22 +7290,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7411,25 +7411,25 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>366</v>
       </c>
       <c r="AP42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7532,25 +7532,25 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>373</v>
       </c>
       <c r="AP43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7656,16 +7656,16 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7777,22 +7777,22 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7898,22 +7898,22 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8016,25 +8016,25 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8143,13 +8143,13 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -8266,13 +8266,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8385,25 +8385,25 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>80</v>
+        <v>416</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>417</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8513,16 +8513,16 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8636,16 +8636,16 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8759,16 +8759,16 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8884,16 +8884,16 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -9002,19 +9002,19 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9129,13 +9129,13 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9252,13 +9252,13 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9377,13 +9377,13 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9492,19 +9492,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9618,22 +9618,22 @@
         <v>476</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>80</v>
+        <v>479</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>480</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9736,19 +9736,19 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9863,13 +9863,13 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9986,13 +9986,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10106,16 +10106,16 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10227,16 +10227,16 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10345,25 +10345,25 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>80</v>
+        <v>507</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM66" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AO66" t="s" s="2">
-        <v>80</v>
+        <v>509</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>509</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -10466,19 +10466,19 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10587,19 +10587,19 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10715,16 +10715,16 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10839,13 +10839,13 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10960,13 +10960,13 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>80</v>
@@ -11081,13 +11081,13 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -11204,13 +11204,13 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -11329,13 +11329,13 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>80</v>
@@ -11447,16 +11447,16 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -11571,13 +11571,13 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11689,16 +11689,16 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>80</v>
@@ -11810,16 +11810,16 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>80</v>
@@ -11931,16 +11931,16 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>80</v>
@@ -12055,13 +12055,13 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>80</v>
@@ -12175,16 +12175,16 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12299,13 +12299,13 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>80</v>
@@ -12422,13 +12422,13 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12547,13 +12547,13 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>80</v>
@@ -12665,16 +12665,16 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12783,22 +12783,22 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>582</v>
+        <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="AN86" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AO86" t="s" s="2">
-        <v>80</v>
+        <v>584</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>584</v>
+        <v>80</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>80</v>
@@ -12907,16 +12907,16 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -13031,13 +13031,13 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>80</v>
@@ -13152,13 +13152,13 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13275,13 +13275,13 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13400,13 +13400,13 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13521,13 +13521,13 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>80</v>
@@ -13642,13 +13642,13 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>80</v>
@@ -13763,13 +13763,13 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>80</v>
@@ -13884,13 +13884,13 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -14003,25 +14003,25 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>80</v>
+        <v>615</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AN96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AP96" t="s" s="2">
-        <v>614</v>
+        <v>80</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" hidden="true">
@@ -14132,13 +14132,13 @@
         <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,7 +520,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
-    <t>299: transform using #not-done on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
+    <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationNameIEN
@@ -862,6 +862,12 @@
   </si>
   <si>
     <t>The visit or admission or other contact between patient and health care provider the immunization was performed as part of.</t>
+  </si>
+  <si>
+    <t>1767: reference from V IMMUNIZATION - VISIT (#9000010.11-.03)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -2278,7 +2284,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="191.34765625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="87.71484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="97.40234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="236.8828125" customWidth="true" bestFit="true"/>
@@ -5503,7 +5509,7 @@
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
@@ -5584,22 +5590,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5607,10 +5613,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5633,16 +5639,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5680,7 +5686,7 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5690,7 +5696,7 @@
         <v>198</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5711,30 +5717,30 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5756,16 +5762,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5815,7 +5821,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5830,33 +5836,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5879,13 +5885,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5936,7 +5942,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5951,10 +5957,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -5963,10 +5969,10 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -5974,10 +5980,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6003,13 +6009,13 @@
         <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6059,7 +6065,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6074,22 +6080,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>80</v>
@@ -6097,10 +6103,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6126,10 +6132,10 @@
         <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6218,10 +6224,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6247,10 +6253,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6337,13 +6343,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6365,16 +6371,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6433,7 +6439,7 @@
         <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>142</v>
@@ -6462,10 +6468,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6583,10 +6589,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6612,10 +6618,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6704,10 +6710,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6733,13 +6739,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6747,7 +6753,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6789,7 +6795,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6827,10 +6833,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6853,13 +6859,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6871,7 +6877,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6910,7 +6916,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6948,10 +6954,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6977,10 +6983,10 @@
         <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7031,7 +7037,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7069,10 +7075,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7098,13 +7104,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7130,13 +7136,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7154,7 +7160,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7178,13 +7184,13 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7192,10 +7198,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7218,13 +7224,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7275,7 +7281,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7296,16 +7302,16 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7313,10 +7319,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7339,13 +7345,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7396,7 +7402,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7411,7 +7417,7 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
@@ -7420,24 +7426,24 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7463,10 +7469,10 @@
         <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7517,7 +7523,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7532,7 +7538,7 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>80</v>
@@ -7541,24 +7547,24 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7581,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7638,7 +7644,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7662,10 +7668,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7676,10 +7682,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7705,10 +7711,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7735,13 +7741,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7759,7 +7765,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7783,24 +7789,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7826,10 +7832,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7856,13 +7862,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7880,7 +7886,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7904,24 +7910,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7944,13 +7950,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8001,7 +8007,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8016,19 +8022,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8039,10 +8045,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8160,10 +8166,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8283,10 +8289,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8309,19 +8315,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8370,7 +8376,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8385,19 +8391,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8408,10 +8414,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8437,20 +8443,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8474,10 +8480,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8495,7 +8501,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8519,10 +8525,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8533,10 +8539,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8562,14 +8568,14 @@
         <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8618,7 +8624,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8642,10 +8648,10 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8656,10 +8662,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8685,14 +8691,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8741,7 +8747,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8750,7 +8756,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8765,10 +8771,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8779,10 +8785,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8808,16 +8814,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8866,7 +8872,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8890,10 +8896,10 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8904,10 +8910,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8930,13 +8936,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8987,7 +8993,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9008,13 +9014,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9025,10 +9031,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9146,10 +9152,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9269,14 +9275,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9298,10 +9304,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9356,7 +9362,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9394,10 +9400,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9423,10 +9429,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9453,13 +9459,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9477,7 +9483,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9498,13 +9504,13 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9515,10 +9521,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9541,16 +9547,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9600,7 +9606,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9615,22 +9621,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9638,10 +9644,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9664,13 +9670,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9721,7 +9727,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9742,13 +9748,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9759,10 +9765,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9880,10 +9886,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10003,10 +10009,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10029,16 +10035,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10088,7 +10094,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10115,7 +10121,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10126,10 +10132,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10152,13 +10158,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10209,7 +10215,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10236,7 +10242,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10247,10 +10253,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10273,13 +10279,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10330,7 +10336,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10345,10 +10351,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10357,7 +10363,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10368,10 +10374,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10397,10 +10403,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10427,13 +10433,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10451,7 +10457,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10472,13 +10478,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10489,10 +10495,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10515,13 +10521,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10572,7 +10578,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10593,7 +10599,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10610,10 +10616,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10639,20 +10645,20 @@
         <v>242</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10697,7 +10703,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10721,7 +10727,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10735,10 +10741,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10764,10 +10770,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10794,13 +10800,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10818,7 +10824,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10856,10 +10862,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10882,13 +10888,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10939,7 +10945,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10951,7 +10957,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10977,10 +10983,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11098,10 +11104,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11221,14 +11227,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11250,10 +11256,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11308,7 +11314,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11346,10 +11352,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11375,10 +11381,10 @@
         <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11429,7 +11435,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11453,7 +11459,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11467,10 +11473,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11496,10 +11502,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11550,7 +11556,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11588,10 +11594,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11614,13 +11620,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11671,7 +11677,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11695,7 +11701,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11709,10 +11715,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11735,13 +11741,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11792,7 +11798,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11816,7 +11822,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11830,10 +11836,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11859,10 +11865,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11889,13 +11895,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11913,7 +11919,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11937,7 +11943,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -11951,10 +11957,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11980,10 +11986,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12010,13 +12016,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12034,7 +12040,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12072,10 +12078,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12098,16 +12104,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12157,7 +12163,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12181,10 +12187,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12195,10 +12201,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12316,10 +12322,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12439,14 +12445,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12468,10 +12474,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12526,7 +12532,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12564,10 +12570,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12590,13 +12596,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12647,7 +12653,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12671,10 +12677,10 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12685,10 +12691,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12711,13 +12717,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12768,7 +12774,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12783,7 +12789,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12792,10 +12798,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12806,10 +12812,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12835,10 +12841,10 @@
         <v>242</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12889,7 +12895,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12913,10 +12919,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12927,10 +12933,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12953,13 +12959,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13010,7 +13016,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13048,10 +13054,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13169,10 +13175,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13292,14 +13298,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13321,10 +13327,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13379,7 +13385,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13417,10 +13423,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13446,10 +13452,10 @@
         <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13500,7 +13506,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13538,10 +13544,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13564,13 +13570,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13621,7 +13627,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13659,10 +13665,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13688,10 +13694,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13718,13 +13724,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13742,7 +13748,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13780,10 +13786,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13806,16 +13812,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13853,7 +13859,7 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
@@ -13863,7 +13869,7 @@
         <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13901,13 +13907,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13932,13 +13938,13 @@
         <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13988,7 +13994,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14003,10 +14009,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14026,10 +14032,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14052,16 +14058,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14111,7 +14117,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (#9000010.11) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (9000010.11) to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -520,7 +520,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
-    <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
+    <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationNameIEN
@@ -555,7 +555,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFimmunizationStatusReason</t>
   </si>
   <si>
-    <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
+    <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -580,7 +580,7 @@
 </t>
   </si>
   <si>
-    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
+    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationNameIEN
@@ -734,7 +734,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1609: source value from IMMUNIZATION LOT - NDC CODE (VA) (#9999999.41-.18)</t>
+    <t>1609: source value from IMMUNIZATION LOT - NDC CODE (VA) (9999999.41-.18)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -833,7 +833,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>333: source value from V IMMUNIZATION - PATIENT NAME (#9000010.11-.02)</t>
+    <t>333: source value from V IMMUNIZATION - PATIENT NAME (9000010.11-.02)</t>
   </si>
   <si>
     <t>Immun.Immunization.PatientIEN</t>
@@ -864,7 +864,7 @@
     <t>The visit or admission or other contact between patient and health care provider the immunization was performed as part of.</t>
   </si>
   <si>
-    <t>1767: reference from V IMMUNIZATION - VISIT (#9000010.11-.03)</t>
+    <t>1767: reference from V IMMUNIZATION - VISIT (9000010.11-.03)</t>
   </si>
   <si>
     <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN</t>
@@ -927,7 +927,7 @@
 </t>
   </si>
   <si>
-    <t>334: source value from V IMMUNIZATION - EVENT DATE AND TIME (#9000010.11-1201)</t>
+    <t>334: source value from V IMMUNIZATION - EVENT DATE AND TIME (9000010.11-1201)</t>
   </si>
   <si>
     <t>Immun.Immunization.EventDateTime</t>
@@ -942,7 +942,7 @@
     <t>The date the occurrence of the immunization was first captured in the record - potentially significantly after the occurrence of the event.</t>
   </si>
   <si>
-    <t>1593: source value from V IMMUNIZATION - DATE/TIME RECORDED (#9000010.11-1205)</t>
+    <t>1593: source value from V IMMUNIZATION - DATE/TIME RECORDED (9000010.11-1205)</t>
   </si>
   <si>
     <t>Immun.Immunization.RecordedDateTime</t>
@@ -966,7 +966,7 @@
     <t>Reflects the “reliability” of the content.</t>
   </si>
   <si>
-    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
+    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (9000010.11-1301)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
@@ -1151,7 +1151,7 @@
     <t>Name of vaccine manufacturer.</t>
   </si>
   <si>
-    <t>339: source value from IMMUNIZATION LOT - MANUFACTURER (#9999999.41-.02)</t>
+    <t>339: source value from IMMUNIZATION LOT - MANUFACTURER (9999999.41-.02)</t>
   </si>
   <si>
     <t>RXA-17</t>
@@ -1172,7 +1172,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>338: source value from IMMUNIZATION LOT - LOT NUMBER (#9999999.41-.01)</t>
+    <t>338: source value from IMMUNIZATION LOT - LOT NUMBER (9999999.41-.01)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1264,7 +1264,7 @@
     <t>The quantity of vaccine product that was administered.</t>
   </si>
   <si>
-    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (#9000010.11-1313 &gt; 757.5-)</t>
+    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (9000010.11-1313 &gt; 757.5-)</t>
   </si>
   <si>
     <t>Immun.Immunization.DoseUnit</t>
@@ -1304,7 +1304,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>340: source value from V IMMUNIZATION - DOSE (#9000010.11-1312)</t>
+    <t>340: source value from V IMMUNIZATION - DOSE (9000010.11-1312)</t>
   </si>
   <si>
     <t>Immun.Immunization.Dosage</t>
@@ -1495,7 +1495,7 @@
     <t>When the individual practitioner who performed the action is known, it is best to send.</t>
   </si>
   <si>
-    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (#9000010.11-1204)</t>
+    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (9000010.11-1204)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizingStaffIEN</t>
@@ -1591,7 +1591,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>343: source value from V IMMUNIZATION - COMMENTS (#9000010.11-81101)</t>
+    <t>343: source value from V IMMUNIZATION - COMMENTS (9000010.11-81101)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationComments</t>
@@ -1916,7 +1916,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>344: source value from V IMMUNIZATION - SERIES (#9000010.11-.04)</t>
+    <t>344: source value from V IMMUNIZATION - SERIES (9000010.11-.04)</t>
   </si>
   <si>
     <t>Immun.Immunization.Series</t>
@@ -2283,7 +2283,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="191.34765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="189.8125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="97.40234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="622">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1018,16 +1018,16 @@
     <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
   </si>
   <si>
+    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource.extension.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension.id</t>
-  </si>
-  <si>
     <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.extension</t>
   </si>
   <si>
@@ -1068,13 +1068,17 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ConceptMap/CMVFimmunizationPrimarySource</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>Immunization.primarySource.value</t>
@@ -6439,7 +6443,7 @@
         <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>142</v>
@@ -6468,10 +6472,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6494,7 +6498,7 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>190</v>
@@ -6560,7 +6564,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>80</v>
@@ -6925,7 +6929,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -6954,10 +6958,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6983,10 +6987,10 @@
         <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7037,7 +7041,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7075,10 +7079,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7104,13 +7108,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7136,13 +7140,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7160,7 +7164,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7187,7 +7191,7 @@
         <v>308</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>310</v>
@@ -7198,10 +7202,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7224,13 +7228,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7281,7 +7285,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7302,16 +7306,16 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7319,10 +7323,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7345,13 +7349,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7402,7 +7406,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7417,7 +7421,7 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
@@ -7426,24 +7430,24 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7469,10 +7473,10 @@
         <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7523,7 +7527,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7538,7 +7542,7 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>80</v>
@@ -7547,24 +7551,24 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7587,13 +7591,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7644,7 +7648,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7668,10 +7672,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7682,10 +7686,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7711,10 +7715,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7741,13 +7745,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7765,7 +7769,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7789,24 +7793,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7832,10 +7836,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7862,13 +7866,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7886,7 +7890,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7910,24 +7914,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7950,13 +7954,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8007,7 +8011,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8022,19 +8026,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8045,10 +8049,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8166,10 +8170,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8289,10 +8293,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8315,19 +8319,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8376,7 +8380,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8391,19 +8395,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8414,10 +8418,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8443,20 +8447,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8480,10 +8484,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8501,7 +8505,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8525,10 +8529,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8539,10 +8543,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8568,14 +8572,14 @@
         <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8624,7 +8628,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8648,10 +8652,10 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8662,10 +8666,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8691,14 +8695,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8747,7 +8751,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8756,7 +8760,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8771,10 +8775,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8785,10 +8789,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8814,16 +8818,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8872,7 +8876,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8896,10 +8900,10 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8910,10 +8914,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8936,13 +8940,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8993,7 +8997,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9014,13 +9018,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9031,10 +9035,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9152,10 +9156,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9275,14 +9279,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9304,10 +9308,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9362,7 +9366,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9400,10 +9404,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9429,10 +9433,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9459,13 +9463,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9483,7 +9487,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9504,13 +9508,13 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9521,10 +9525,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9547,16 +9551,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9606,7 +9610,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9621,22 +9625,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9644,10 +9648,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9670,13 +9674,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9727,7 +9731,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9748,13 +9752,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9765,10 +9769,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9886,10 +9890,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10009,10 +10013,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10035,16 +10039,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10094,7 +10098,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10121,7 +10125,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10132,10 +10136,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10161,10 +10165,10 @@
         <v>292</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10215,7 +10219,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10242,7 +10246,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10253,10 +10257,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10279,13 +10283,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10336,7 +10340,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10351,10 +10355,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10363,7 +10367,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10374,10 +10378,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10403,10 +10407,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10433,13 +10437,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10457,7 +10461,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10478,13 +10482,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10495,10 +10499,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10521,13 +10525,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10578,7 +10582,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10599,7 +10603,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10616,10 +10620,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10645,20 +10649,20 @@
         <v>242</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10703,7 +10707,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10727,7 +10731,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10741,10 +10745,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10770,10 +10774,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10800,13 +10804,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10824,7 +10828,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10862,10 +10866,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10888,13 +10892,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10945,7 +10949,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10957,7 +10961,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10983,10 +10987,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11104,10 +11108,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11227,14 +11231,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11256,10 +11260,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11314,7 +11318,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11352,10 +11356,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11381,10 +11385,10 @@
         <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11435,7 +11439,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11459,7 +11463,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11473,10 +11477,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11502,10 +11506,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11556,7 +11560,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11594,10 +11598,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11623,10 +11627,10 @@
         <v>292</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11677,7 +11681,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11701,7 +11705,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11715,10 +11719,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11744,10 +11748,10 @@
         <v>292</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11798,7 +11802,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11822,7 +11826,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11836,10 +11840,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11865,10 +11869,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11895,13 +11899,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11919,7 +11923,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11943,7 +11947,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -11957,10 +11961,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11986,10 +11990,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12016,13 +12020,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12040,7 +12044,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12078,10 +12082,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12104,16 +12108,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12163,7 +12167,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12187,10 +12191,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12201,10 +12205,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12322,10 +12326,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12445,14 +12449,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12474,10 +12478,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12532,7 +12536,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12570,10 +12574,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12599,10 +12603,10 @@
         <v>292</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12653,7 +12657,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12677,7 +12681,7 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>287</v>
@@ -12691,10 +12695,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12717,13 +12721,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12774,7 +12778,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12789,7 +12793,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12798,10 +12802,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12812,10 +12816,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12841,10 +12845,10 @@
         <v>242</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12895,7 +12899,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12919,10 +12923,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12933,10 +12937,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12959,13 +12963,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13016,7 +13020,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13054,10 +13058,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13175,10 +13179,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13298,14 +13302,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13327,10 +13331,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13385,7 +13389,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13423,10 +13427,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13452,10 +13456,10 @@
         <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13506,7 +13510,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13544,10 +13548,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13570,13 +13574,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13627,7 +13631,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13665,10 +13669,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13694,10 +13698,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13724,13 +13728,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13748,7 +13752,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13786,10 +13790,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13812,16 +13816,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13869,7 +13873,7 @@
         <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13907,13 +13911,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13938,13 +13942,13 @@
         <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13994,7 +13998,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14009,10 +14013,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14032,10 +14036,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14058,16 +14062,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14117,7 +14121,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="627">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -737,6 +737,9 @@
     <t>1609: source value from IMMUNIZATION LOT - NDC CODE (VA) (9999999.41-.18)</t>
   </si>
   <si>
+    <t>Dim.ImmunizationLot.NDCCodeVAText</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
@@ -1130,6 +1133,13 @@
     <t>The service delivery location where the vaccine administration occurred.</t>
   </si>
   <si>
+    <t>1801: reference from V IMMUNIZATION - VISIT &gt; VISIT - HOSPITAL LOCATION (9000010.11-.03 &gt; 9000010-.22)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN
+Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
+  </si>
+  <si>
     <t>Event.location</t>
   </si>
   <si>
@@ -1158,6 +1168,9 @@
     <t>339: source value from IMMUNIZATION LOT - MANUFACTURER (9999999.41-.02)</t>
   </si>
   <si>
+    <t>Dim.ImmunizationLot.ImmunizationManufacturerIEN,Dim.ImmunizationLot.ImmunizationManufacturerSID</t>
+  </si>
+  <si>
     <t>RXA-17</t>
   </si>
   <si>
@@ -1177,6 +1190,9 @@
   </si>
   <si>
     <t>338: source value from IMMUNIZATION LOT - LOT NUMBER (9999999.41-.01)</t>
+  </si>
+  <si>
+    <t>Dim.ImmunizationLot.ImmunizationLot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -2288,7 +2304,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="189.8125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="97.40234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="98.1015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="236.8828125" customWidth="true" bestFit="true"/>
@@ -4982,16 +4998,16 @@
         <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5002,10 +5018,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5031,14 +5047,14 @@
         <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5087,7 +5103,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5111,10 +5127,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5125,10 +5141,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5151,19 +5167,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5212,7 +5228,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5236,10 +5252,10 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5250,10 +5266,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5279,16 +5295,16 @@
         <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5337,7 +5353,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5361,10 +5377,10 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5375,14 +5391,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5401,13 +5417,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5458,7 +5474,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5473,22 +5489,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5496,10 +5512,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5522,13 +5538,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5579,7 +5595,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5594,22 +5610,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5617,10 +5633,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5643,16 +5659,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5690,7 +5706,7 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5700,7 +5716,7 @@
         <v>198</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5721,30 +5737,30 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5766,16 +5782,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5825,7 +5841,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5840,33 +5856,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5889,13 +5905,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5946,7 +5962,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5961,10 +5977,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -5973,10 +5989,10 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -5984,10 +6000,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6010,16 +6026,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6069,7 +6085,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6084,22 +6100,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>80</v>
@@ -6107,10 +6123,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6136,10 +6152,10 @@
         <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6228,10 +6244,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6257,10 +6273,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6347,13 +6363,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6375,16 +6391,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6472,10 +6488,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6564,7 +6580,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>80</v>
@@ -6593,10 +6609,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6622,10 +6638,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6714,10 +6730,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6743,13 +6759,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6757,7 +6773,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6799,7 +6815,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6837,10 +6853,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6863,13 +6879,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6881,7 +6897,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6920,7 +6936,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6929,7 +6945,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -6958,10 +6974,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6984,13 +7000,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7041,7 +7057,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7079,10 +7095,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7108,13 +7124,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7140,13 +7156,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7164,7 +7180,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7188,13 +7204,13 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7202,10 +7218,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7219,7 +7235,7 @@
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>80</v>
@@ -7228,13 +7244,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7285,7 +7301,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7300,22 +7316,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7323,10 +7339,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7349,13 +7365,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7406,7 +7422,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7421,33 +7437,33 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7473,10 +7489,10 @@
         <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7527,7 +7543,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7542,33 +7558,33 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7591,13 +7607,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7648,7 +7664,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7672,10 +7688,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7686,10 +7702,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7715,10 +7731,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7745,13 +7761,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7769,7 +7785,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7793,24 +7809,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7836,10 +7852,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7866,13 +7882,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7890,7 +7906,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7914,24 +7930,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7954,13 +7970,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8011,7 +8027,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8026,19 +8042,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8049,10 +8065,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8170,10 +8186,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8293,10 +8309,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8319,19 +8335,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8380,7 +8396,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8395,19 +8411,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8418,10 +8434,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8447,20 +8463,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8484,10 +8500,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8505,7 +8521,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8529,10 +8545,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8543,10 +8559,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8572,14 +8588,14 @@
         <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8628,7 +8644,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8652,10 +8668,10 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8666,10 +8682,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8695,14 +8711,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8751,7 +8767,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8760,7 +8776,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8775,10 +8791,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8789,10 +8805,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8818,16 +8834,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8876,7 +8892,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8900,10 +8916,10 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8914,10 +8930,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8940,13 +8956,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8997,7 +9013,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9018,13 +9034,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9035,10 +9051,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9156,10 +9172,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9279,14 +9295,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9308,10 +9324,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9366,7 +9382,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9404,10 +9420,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9433,10 +9449,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9463,31 +9479,31 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9508,13 +9524,13 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9525,10 +9541,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9551,16 +9567,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9610,7 +9626,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9625,22 +9641,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9648,10 +9664,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9674,13 +9690,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9731,7 +9747,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9752,13 +9768,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9769,10 +9785,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9890,10 +9906,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10013,10 +10029,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10039,16 +10055,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10098,7 +10114,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10125,7 +10141,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10136,10 +10152,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10162,13 +10178,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10219,7 +10235,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10246,7 +10262,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10257,10 +10273,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10283,13 +10299,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10340,7 +10356,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10355,10 +10371,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10367,7 +10383,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10378,10 +10394,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10407,10 +10423,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10437,13 +10453,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10461,7 +10477,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10482,13 +10498,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10499,10 +10515,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10525,13 +10541,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10582,7 +10598,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10603,7 +10619,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10620,10 +10636,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10646,23 +10662,23 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10707,7 +10723,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10731,7 +10747,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10745,10 +10761,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10774,10 +10790,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10804,13 +10820,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10828,7 +10844,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10866,10 +10882,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10892,13 +10908,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10949,7 +10965,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10961,7 +10977,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10987,10 +11003,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11108,10 +11124,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11231,14 +11247,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11260,10 +11276,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11318,7 +11334,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11356,10 +11372,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11385,10 +11401,10 @@
         <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11439,7 +11455,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11463,7 +11479,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11477,10 +11493,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11506,10 +11522,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11560,7 +11576,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11598,10 +11614,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11624,13 +11640,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11681,7 +11697,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11705,7 +11721,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11719,10 +11735,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11745,13 +11761,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11802,7 +11818,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11826,7 +11842,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11840,10 +11856,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11869,10 +11885,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11899,13 +11915,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11923,7 +11939,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11947,7 +11963,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -11961,10 +11977,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11990,10 +12006,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12020,13 +12036,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12044,7 +12060,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12082,10 +12098,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12108,16 +12124,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12167,7 +12183,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12191,10 +12207,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12205,10 +12221,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12326,10 +12342,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12449,14 +12465,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12478,10 +12494,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12536,7 +12552,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12574,10 +12590,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12600,13 +12616,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12657,7 +12673,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12681,10 +12697,10 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12695,10 +12711,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12721,13 +12737,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12778,7 +12794,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12793,7 +12809,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12802,10 +12818,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12816,10 +12832,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12842,13 +12858,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12899,7 +12915,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12923,10 +12939,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12937,10 +12953,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12963,13 +12979,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13020,7 +13036,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13058,10 +13074,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13179,10 +13195,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13302,14 +13318,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13331,10 +13347,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13389,7 +13405,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13427,10 +13443,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13456,10 +13472,10 @@
         <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13510,7 +13526,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13548,10 +13564,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13574,13 +13590,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13631,7 +13647,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13669,10 +13685,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13698,10 +13714,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13728,13 +13744,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13752,7 +13768,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13790,10 +13806,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13816,16 +13832,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13863,7 +13879,7 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
@@ -13873,7 +13889,7 @@
         <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13911,13 +13927,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="B96" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="C96" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13942,13 +13958,13 @@
         <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13998,7 +14014,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14013,10 +14029,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14036,10 +14052,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14062,16 +14078,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14121,7 +14137,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="632">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,7 +689,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/sid/ndc</t>
+  </si>
+  <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1609-1: fixed value = http://hl7.org/fhir/sid/ndc</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -813,6 +819,9 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>332-1: undefined case not null</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
@@ -1381,6 +1390,13 @@
     <t>Quantity.unit</t>
   </si>
   <si>
+    <t>464-1: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - DISPLAY (9000010.11-1313 &gt; 757.5-.01)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.DoseUnit
+Dim.UCUMCode.DescriptionOfTheUnit</t>
+  </si>
+  <si>
     <t>(see OBX.6 etc.) / CQ.2</t>
   </si>
   <si>
@@ -1427,6 +1443,13 @@
     <t>Quantity.code</t>
   </si>
   <si>
+    <t>464-2: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - UCUM CODE (9000010.11-1313 &gt; 757.5-1)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.DoseUnit
+Dim.UCUMCode.UCUMCode</t>
+  </si>
+  <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
@@ -1513,12 +1536,6 @@
   </si>
   <si>
     <t>When the individual practitioner who performed the action is known, it is best to send.</t>
-  </si>
-  <si>
-    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (9000010.11-1204)</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizingStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -4664,7 +4681,7 @@
         <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -4695,7 +4712,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -4734,7 +4751,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4749,7 +4766,7 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
@@ -4758,10 +4775,10 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4772,10 +4789,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4801,13 +4818,13 @@
         <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4857,7 +4874,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4881,10 +4898,10 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4895,10 +4912,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4924,14 +4941,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4980,7 +4997,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4995,19 +5012,19 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5018,10 +5035,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5047,14 +5064,14 @@
         <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5103,7 +5120,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5127,10 +5144,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5141,10 +5158,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5167,19 +5184,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5228,7 +5245,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5252,10 +5269,10 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5266,10 +5283,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5283,7 +5300,7 @@
         <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
@@ -5295,16 +5312,16 @@
         <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5353,7 +5370,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5368,7 +5385,7 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
@@ -5377,10 +5394,10 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5391,14 +5408,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5417,13 +5434,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5474,7 +5491,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5489,22 +5506,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5512,10 +5529,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5538,13 +5555,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5595,7 +5612,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5610,22 +5627,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5633,10 +5650,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5659,16 +5676,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5706,7 +5723,7 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5716,7 +5733,7 @@
         <v>198</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5737,30 +5754,30 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5782,16 +5799,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5841,7 +5858,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5856,33 +5873,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5905,13 +5922,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5962,7 +5979,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5977,10 +5994,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -5989,10 +6006,10 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -6000,10 +6017,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6026,16 +6043,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6085,7 +6102,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6100,22 +6117,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>80</v>
@@ -6123,10 +6140,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6152,10 +6169,10 @@
         <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6244,10 +6261,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6273,10 +6290,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6363,13 +6380,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="C34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6391,16 +6408,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6488,10 +6505,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6580,7 +6597,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>80</v>
@@ -6609,10 +6626,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6638,10 +6655,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6730,10 +6747,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6759,13 +6776,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6773,7 +6790,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6815,7 +6832,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6853,10 +6870,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6879,13 +6896,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6897,7 +6914,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6936,7 +6953,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6945,7 +6962,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -6974,10 +6991,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7000,13 +7017,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7057,7 +7074,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7095,10 +7112,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7124,13 +7141,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7156,13 +7173,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7180,7 +7197,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7204,13 +7221,13 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7218,10 +7235,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7244,13 +7261,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7301,7 +7318,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7316,22 +7333,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7339,10 +7356,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7365,13 +7382,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7422,7 +7439,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7437,33 +7454,33 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7489,10 +7506,10 @@
         <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7543,7 +7560,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7558,33 +7575,33 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7607,13 +7624,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7664,7 +7681,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7688,10 +7705,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7702,10 +7719,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7731,10 +7748,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7761,31 +7778,31 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7809,24 +7826,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7852,10 +7869,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7882,31 +7899,31 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7930,24 +7947,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7970,13 +7987,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8027,7 +8044,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8042,19 +8059,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8065,10 +8082,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8186,10 +8203,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8309,10 +8326,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8335,19 +8352,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8396,7 +8413,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8411,19 +8428,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8434,10 +8451,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8463,20 +8480,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8500,10 +8517,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8521,7 +8538,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8545,10 +8562,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8559,10 +8576,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8576,7 +8593,7 @@
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8588,14 +8605,14 @@
         <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8644,7 +8661,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8659,19 +8676,19 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8682,10 +8699,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8711,14 +8728,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8767,7 +8784,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8776,7 +8793,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8791,10 +8808,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8805,10 +8822,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8822,7 +8839,7 @@
         <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
@@ -8834,16 +8851,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8892,7 +8909,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8907,19 +8924,19 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>461</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>462</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8930,10 +8947,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8956,13 +8973,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9013,7 +9030,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9034,13 +9051,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9051,10 +9068,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9172,10 +9189,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9295,14 +9312,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9324,10 +9341,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9382,7 +9399,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9420,10 +9437,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9449,10 +9466,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9479,13 +9496,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9503,7 +9520,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9524,13 +9541,13 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9541,10 +9558,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9558,7 +9575,7 @@
         <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
@@ -9567,16 +9584,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9626,7 +9643,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9641,22 +9658,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>484</v>
+        <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9664,10 +9681,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9690,13 +9707,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9747,7 +9764,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9768,13 +9785,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9785,10 +9802,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9906,10 +9923,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10029,10 +10046,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10055,16 +10072,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10114,7 +10131,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10141,7 +10158,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10152,10 +10169,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10178,13 +10195,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10235,7 +10252,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10262,7 +10279,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10273,10 +10290,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10299,13 +10316,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10356,7 +10373,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10371,10 +10388,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10383,7 +10400,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10394,10 +10411,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10423,10 +10440,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10453,13 +10470,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10477,7 +10494,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10498,13 +10515,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10515,10 +10532,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10541,13 +10558,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10598,7 +10615,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10619,7 +10636,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10636,10 +10653,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10662,23 +10679,23 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10723,7 +10740,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10747,7 +10764,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10761,10 +10778,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10790,10 +10807,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10820,13 +10837,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10844,7 +10861,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10882,10 +10899,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10908,13 +10925,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10965,7 +10982,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10977,7 +10994,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -11003,10 +11020,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11124,10 +11141,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11247,14 +11264,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11276,10 +11293,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11334,7 +11351,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11372,10 +11389,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11401,10 +11418,10 @@
         <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11455,7 +11472,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11479,7 +11496,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11493,10 +11510,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11522,10 +11539,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11576,7 +11593,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11614,10 +11631,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11640,13 +11657,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11697,7 +11714,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11721,7 +11738,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11735,10 +11752,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11761,13 +11778,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11818,7 +11835,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11842,7 +11859,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11856,10 +11873,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11885,10 +11902,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11915,13 +11932,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11939,7 +11956,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11963,7 +11980,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -11977,10 +11994,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12006,10 +12023,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12036,13 +12053,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12060,7 +12077,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12098,10 +12115,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12124,16 +12141,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12183,7 +12200,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12207,10 +12224,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12221,10 +12238,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12342,10 +12359,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12465,14 +12482,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12494,10 +12511,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12552,7 +12569,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12590,10 +12607,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12616,13 +12633,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12673,7 +12690,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12697,10 +12714,10 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12711,10 +12728,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12737,13 +12754,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12794,7 +12811,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12809,7 +12826,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12818,10 +12835,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12832,10 +12849,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12858,13 +12875,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12915,7 +12932,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12939,10 +12956,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12953,10 +12970,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12979,13 +12996,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13036,7 +13053,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13074,10 +13091,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13195,10 +13212,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13318,14 +13335,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13347,10 +13364,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13405,7 +13422,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13443,10 +13460,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13472,10 +13489,10 @@
         <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13526,7 +13543,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13564,10 +13581,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13590,13 +13607,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13647,7 +13664,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13685,10 +13702,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13714,10 +13731,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13744,13 +13761,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13768,7 +13785,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13806,10 +13823,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13832,16 +13849,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13879,7 +13896,7 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
@@ -13889,7 +13906,7 @@
         <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13927,13 +13944,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="B96" t="s" s="2">
-        <v>615</v>
-      </c>
       <c r="C96" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13958,13 +13975,13 @@
         <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14014,7 +14031,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14029,10 +14046,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14052,10 +14069,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14078,16 +14095,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14137,7 +14154,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1390,7 +1390,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>464-1: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - DISPLAY (9000010.11-1313 &gt; 757.5-.01)</t>
+    <t>464-1: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - DESCRIPTION OF THE UNIT (9000010.11-1313 &gt; 757.5-.01)</t>
   </si>
   <si>
     <t>Immun.Immunization.DoseUnit
@@ -1507,6 +1507,14 @@
     <t>Describes the type of performance (e.g. ordering provider, administering provider, etc.).</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0443"/&gt;
+    &lt;code value="AP"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -1516,6 +1524,9 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-function</t>
   </si>
   <si>
+    <t>342-1: fixed value = http://terminology.hl7.org/CodeSystem/v2-0443#AP</t>
+  </si>
+  <si>
     <t>Event.performer.function</t>
   </si>
   <si>
@@ -1525,7 +1536,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Practitioner)
 </t>
   </si>
   <si>
@@ -1536,6 +1547,12 @@
   </si>
   <si>
     <t>When the individual practitioner who performed the action is known, it is best to send.</t>
+  </si>
+  <si>
+    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (9000010.11-1204)</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizingStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -9454,7 +9471,7 @@
         <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -9481,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>80</v>
@@ -9496,13 +9513,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9535,19 +9552,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9558,10 +9575,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9575,7 +9592,7 @@
         <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
@@ -9584,16 +9601,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9643,7 +9660,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9658,22 +9675,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>493</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>80</v>
+        <v>494</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9681,10 +9698,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9707,13 +9724,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9764,7 +9781,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9785,13 +9802,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9802,10 +9819,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9923,10 +9940,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10046,10 +10063,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10072,16 +10089,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10131,7 +10148,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10158,7 +10175,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10169,10 +10186,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10198,10 +10215,10 @@
         <v>296</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10252,7 +10269,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10279,7 +10296,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10290,10 +10307,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10316,13 +10333,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10373,7 +10390,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10388,10 +10405,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10400,7 +10417,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10411,10 +10428,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10440,10 +10457,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10473,28 +10490,28 @@
         <v>355</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="Z67" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10515,13 +10532,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10532,10 +10549,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10558,13 +10575,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10615,7 +10632,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10636,7 +10653,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10653,10 +10670,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10682,65 +10699,65 @@
         <v>245</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="R69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10764,7 +10781,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10778,10 +10795,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10807,10 +10824,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10840,28 +10857,28 @@
         <v>355</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="Z70" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10899,10 +10916,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10928,10 +10945,10 @@
         <v>465</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10982,7 +10999,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10994,7 +11011,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -11020,10 +11037,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11141,10 +11158,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11264,10 +11281,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11389,10 +11406,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11418,10 +11435,10 @@
         <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11472,7 +11489,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11496,7 +11513,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11510,10 +11527,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11539,10 +11556,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11593,7 +11610,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11631,10 +11648,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11660,10 +11677,10 @@
         <v>296</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11714,7 +11731,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11738,7 +11755,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11752,10 +11769,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11781,10 +11798,10 @@
         <v>296</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11835,7 +11852,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11859,7 +11876,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11873,10 +11890,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11902,10 +11919,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11935,28 +11952,28 @@
         <v>355</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="Z79" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11980,7 +11997,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -11994,10 +12011,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12023,10 +12040,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12056,28 +12073,28 @@
         <v>355</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="Z80" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12115,10 +12132,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12144,13 +12161,13 @@
         <v>465</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12200,7 +12217,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12224,10 +12241,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12238,10 +12255,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12359,10 +12376,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12482,10 +12499,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12607,10 +12624,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12636,10 +12653,10 @@
         <v>296</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12690,7 +12707,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12714,7 +12731,7 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>291</v>
@@ -12728,10 +12745,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12754,13 +12771,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12811,7 +12828,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12826,7 +12843,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12835,10 +12852,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12849,10 +12866,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12878,10 +12895,10 @@
         <v>245</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12932,7 +12949,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12956,10 +12973,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12970,10 +12987,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12999,10 +13016,10 @@
         <v>465</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13053,7 +13070,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13091,10 +13108,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13212,10 +13229,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13335,10 +13352,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13460,10 +13477,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13489,10 +13506,10 @@
         <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13543,7 +13560,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13581,10 +13598,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13610,10 +13627,10 @@
         <v>370</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13664,7 +13681,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13702,10 +13719,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13731,10 +13748,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13764,28 +13781,28 @@
         <v>355</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="Z94" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13823,10 +13840,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13849,16 +13866,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13906,7 +13923,7 @@
         <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13944,13 +13961,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13975,13 +13992,13 @@
         <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14031,7 +14048,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14046,10 +14063,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14069,10 +14086,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14095,16 +14112,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14154,7 +14171,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -740,7 +740,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1609: source value from IMMUNIZATION LOT - NDC CODE (VA) (9999999.41-.18)</t>
+    <t>1609: source value from V IMMUNIZATION - IMMUNIZATION LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.NDCCodeVAText</t>
@@ -1174,7 +1174,7 @@
     <t>Name of vaccine manufacturer.</t>
   </si>
   <si>
-    <t>339: source value from IMMUNIZATION LOT - MANUFACTURER (9999999.41-.02)</t>
+    <t>339: source value from V IMMUNIZATION - IMMUNIZATION LOT &gt; IMMUNIZATION LOT - MANUFACTURER (9000010.11-.05 &gt; 9999999.41-.02)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.ImmunizationManufacturerIEN,Dim.ImmunizationLot.ImmunizationManufacturerSID</t>
@@ -1198,7 +1198,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>338: source value from IMMUNIZATION LOT - LOT NUMBER (9999999.41-.01)</t>
+    <t>338: source value from V IMMUNIZATION - IMMUNIZATION LOT &gt; IMMUNIZATION LOT - LOT NUMBER (9000010.11-.05 &gt; 9999999.41-.01)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.ImmunizationLot</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1645,7 +1645,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>343: source value from V IMMUNIZATION - COMMENTS (9000010.11-81101)</t>
+    <t>343: source value from null (9000010.11-81101)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationComments</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1536,7 +1536,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1645,7 +1645,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>343: source value from null (9000010.11-81101)</t>
+    <t>343: source value from V IMMUNIZATION - COMMENTS (9000010.11-81101)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationComments</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -740,7 +740,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1609: source value from V IMMUNIZATION - IMMUNIZATION LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
+    <t>1609: source value from V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.NDCCodeVAText</t>
@@ -1174,7 +1174,7 @@
     <t>Name of vaccine manufacturer.</t>
   </si>
   <si>
-    <t>339: source value from V IMMUNIZATION - IMMUNIZATION LOT &gt; IMMUNIZATION LOT - MANUFACTURER (9000010.11-.05 &gt; 9999999.41-.02)</t>
+    <t>339: source value from V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - MANUFACTURER (9000010.11-.05 &gt; 9999999.41-.02)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.ImmunizationManufacturerIEN,Dim.ImmunizationLot.ImmunizationManufacturerSID</t>
@@ -1198,7 +1198,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>338: source value from V IMMUNIZATION - IMMUNIZATION LOT &gt; IMMUNIZATION LOT - LOT NUMBER (9000010.11-.05 &gt; 9999999.41-.01)</t>
+    <t>338: source value from V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - LOT NUMBER (9000010.11-.05 &gt; 9999999.41-.01)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.ImmunizationLot</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="635">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -580,11 +580,7 @@
 </t>
   </si>
   <si>
-    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizationNameIEN
-Dim.ImmunizationName.CVXCode</t>
+    <t>528: terminologyMaps using VF_inferredCVX on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -4048,30 +4044,30 @@
         <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4094,13 +4090,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4151,34 +4147,34 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -4189,10 +4185,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4221,7 +4217,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -4262,19 +4258,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4301,7 +4297,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -4312,10 +4308,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4338,19 +4334,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4399,7 +4395,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4423,10 +4419,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4437,10 +4433,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4463,13 +4459,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4520,34 +4516,34 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4590,7 +4586,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4631,19 +4627,19 @@
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE19" t="s" s="2">
+      <c r="AF19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4670,7 +4666,7 @@
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4681,10 +4677,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4710,16 +4706,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4729,46 +4725,46 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4783,19 +4779,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4806,10 +4802,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4832,16 +4828,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4891,7 +4887,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4915,10 +4911,10 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4929,10 +4925,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4958,14 +4954,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5014,7 +5010,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5029,19 +5025,19 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5052,10 +5048,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5078,17 +5074,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5137,7 +5133,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5161,10 +5157,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5175,10 +5171,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5201,19 +5197,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5262,7 +5258,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5286,10 +5282,10 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5300,10 +5296,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5326,19 +5322,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5387,7 +5383,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5402,19 +5398,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5425,14 +5421,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5451,13 +5447,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5508,7 +5504,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5523,22 +5519,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5546,10 +5542,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5572,13 +5568,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5629,7 +5625,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5644,22 +5640,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5667,10 +5663,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5693,16 +5689,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5740,17 +5736,17 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5771,30 +5767,30 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5816,16 +5812,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5875,7 +5871,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5890,33 +5886,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="AM29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AP29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5939,13 +5935,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5996,7 +5992,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6011,22 +6007,22 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -6034,10 +6030,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6060,16 +6056,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6119,7 +6115,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6134,22 +6130,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>80</v>
@@ -6157,10 +6153,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6183,13 +6179,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6240,7 +6236,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6278,10 +6274,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6307,10 +6303,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6349,17 +6345,17 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6397,13 +6393,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6425,16 +6421,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6484,7 +6480,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6522,10 +6518,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6551,10 +6547,10 @@
         <v>93</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6605,34 +6601,34 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6643,10 +6639,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6672,10 +6668,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6714,19 +6710,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AC36" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC36" t="s" s="2">
+      <c r="AD36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE36" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AD36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE36" t="s" s="2">
+      <c r="AF36" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6764,10 +6760,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6793,13 +6789,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6807,49 +6803,49 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6887,10 +6883,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6913,13 +6909,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6931,55 +6927,55 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="T38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF38" t="s" s="2">
+      <c r="AG38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI38" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7008,10 +7004,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7034,13 +7030,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7091,7 +7087,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7129,10 +7125,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7158,13 +7154,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7190,14 +7186,14 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
       </c>
@@ -7214,7 +7210,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7238,13 +7234,13 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7252,10 +7248,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7278,13 +7274,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7335,7 +7331,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7350,22 +7346,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7373,10 +7369,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7399,13 +7395,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7456,7 +7452,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7471,33 +7467,33 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7520,13 +7516,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7577,7 +7573,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7592,33 +7588,33 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7641,13 +7637,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7698,7 +7694,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7722,10 +7718,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7736,10 +7732,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7765,10 +7761,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7795,14 +7791,14 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7819,7 +7815,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7843,24 +7839,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7886,10 +7882,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7916,14 +7912,14 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7940,7 +7936,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7964,24 +7960,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8004,13 +8000,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8061,7 +8057,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8076,19 +8072,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8099,10 +8095,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8125,13 +8121,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8182,34 +8178,34 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -8220,10 +8216,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8252,7 +8248,7 @@
         <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -8293,19 +8289,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AC49" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC49" t="s" s="2">
+      <c r="AD49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE49" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AD49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE49" t="s" s="2">
+      <c r="AF49" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8332,7 +8328,7 @@
         <v>80</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8343,10 +8339,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8369,19 +8365,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8430,7 +8426,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8445,19 +8441,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8468,10 +8464,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8497,20 +8493,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q51" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q51" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8534,28 +8530,28 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8579,10 +8575,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8593,10 +8589,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8619,17 +8615,17 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8678,7 +8674,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8693,19 +8689,19 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8716,10 +8712,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8745,14 +8741,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8801,16 +8797,16 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI53" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8825,10 +8821,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8839,10 +8835,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8868,16 +8864,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8926,7 +8922,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8941,19 +8937,19 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8964,10 +8960,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8990,13 +8986,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9047,7 +9043,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9068,13 +9064,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9085,10 +9081,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9111,13 +9107,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9168,34 +9164,34 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9206,10 +9202,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9238,7 +9234,7 @@
         <v>138</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -9291,7 +9287,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9318,7 +9314,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9329,14 +9325,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9358,10 +9354,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9416,7 +9412,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9454,10 +9450,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9483,10 +9479,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9498,29 +9494,29 @@
         <v>80</v>
       </c>
       <c r="S59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="T59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X59" t="s" s="2">
+      <c r="Y59" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9537,7 +9533,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9552,19 +9548,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9575,10 +9571,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9601,16 +9597,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9660,7 +9656,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9675,22 +9671,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9698,10 +9694,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9724,13 +9720,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9781,7 +9777,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9802,13 +9798,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9819,10 +9815,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9845,13 +9841,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9902,34 +9898,34 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9940,10 +9936,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9972,7 +9968,7 @@
         <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -10013,19 +10009,19 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AC63" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC63" t="s" s="2">
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AD63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE63" t="s" s="2">
+      <c r="AF63" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10052,7 +10048,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10063,10 +10059,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10089,16 +10085,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10148,7 +10144,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10175,7 +10171,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10186,10 +10182,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10212,13 +10208,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10269,7 +10265,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10296,7 +10292,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10307,10 +10303,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10333,13 +10329,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10390,7 +10386,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10405,10 +10401,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10417,7 +10413,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10428,10 +10424,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10457,10 +10453,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10487,14 +10483,14 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
       </c>
@@ -10511,7 +10507,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10532,13 +10528,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10549,10 +10545,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10575,13 +10571,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10632,7 +10628,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10653,7 +10649,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10670,10 +10666,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10696,23 +10692,23 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10757,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10781,7 +10777,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10795,10 +10791,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10824,10 +10820,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10854,14 +10850,14 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>548</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10878,7 +10874,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10916,10 +10912,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10942,13 +10938,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10999,7 +10995,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11011,7 +11007,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -11037,10 +11033,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11063,13 +11059,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11120,34 +11116,34 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -11158,10 +11154,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11190,7 +11186,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -11243,7 +11239,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11270,7 +11266,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -11281,14 +11277,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11310,10 +11306,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11368,7 +11364,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11406,10 +11402,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11432,13 +11428,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11489,7 +11485,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11513,7 +11509,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11527,10 +11523,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11556,10 +11552,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11610,7 +11606,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11648,10 +11644,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11674,13 +11670,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11731,7 +11727,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11755,7 +11751,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11769,10 +11765,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11795,13 +11791,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11852,7 +11848,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11876,7 +11872,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11890,10 +11886,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11919,10 +11915,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11949,14 +11945,14 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z79" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11973,7 +11969,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11997,7 +11993,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -12011,10 +12007,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12040,10 +12036,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12070,14 +12066,14 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
       </c>
@@ -12094,7 +12090,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12132,10 +12128,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12158,16 +12154,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12217,7 +12213,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12241,10 +12237,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12255,10 +12251,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12281,13 +12277,13 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12338,34 +12334,34 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>80</v>
@@ -12376,10 +12372,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12408,7 +12404,7 @@
         <v>138</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12461,7 +12457,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12488,7 +12484,7 @@
         <v>80</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12499,14 +12495,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12528,10 +12524,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12586,7 +12582,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12624,10 +12620,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12650,13 +12646,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12707,7 +12703,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12731,10 +12727,10 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12745,10 +12741,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12771,13 +12767,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12828,7 +12824,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12843,19 +12839,19 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AL86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12866,10 +12862,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12892,13 +12888,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12949,7 +12945,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12973,10 +12969,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12987,10 +12983,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13013,13 +13009,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13070,7 +13066,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13108,10 +13104,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13134,13 +13130,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13191,34 +13187,34 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13229,10 +13225,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13261,7 +13257,7 @@
         <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>140</v>
@@ -13314,7 +13310,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13341,7 +13337,7 @@
         <v>80</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13352,14 +13348,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13381,10 +13377,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13439,7 +13435,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13477,10 +13473,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13503,13 +13499,13 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13560,7 +13556,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13598,10 +13594,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13624,13 +13620,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13681,7 +13677,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13719,10 +13715,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13748,10 +13744,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13778,14 +13774,14 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>623</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
       </c>
@@ -13802,7 +13798,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13840,10 +13836,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13866,16 +13862,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13913,17 +13909,17 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13961,13 +13957,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13989,16 +13985,16 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14048,7 +14044,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14063,10 +14059,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14086,10 +14082,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14112,16 +14108,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>635</v>
-      </c>
       <c r="N97" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14171,7 +14167,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -580,7 +580,11 @@
 </t>
   </si>
   <si>
-    <t>528: terminologyMaps using VF_inferredCVX on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
+    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationNameIEN
+Dim.ImmunizationName.CVXCode</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -4044,30 +4048,30 @@
         <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4090,13 +4094,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4147,7 +4151,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4174,7 +4178,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -4185,10 +4189,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4217,7 +4221,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -4258,19 +4262,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4297,7 +4301,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -4308,10 +4312,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4334,19 +4338,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4395,7 +4399,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4419,10 +4423,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4433,10 +4437,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4459,13 +4463,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4516,7 +4520,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4543,7 +4547,7 @@
         <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4586,7 +4590,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4627,19 +4631,19 @@
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4666,7 +4670,7 @@
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4677,10 +4681,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4706,16 +4710,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4725,7 +4729,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -4764,7 +4768,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4779,7 +4783,7 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
@@ -4788,10 +4792,10 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4802,10 +4806,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4828,16 +4832,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4887,7 +4891,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4911,10 +4915,10 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4925,10 +4929,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4954,14 +4958,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5010,7 +5014,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5025,19 +5029,19 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5048,10 +5052,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5074,17 +5078,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5133,7 +5137,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5157,10 +5161,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5171,10 +5175,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5197,19 +5201,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5258,7 +5262,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5282,10 +5286,10 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5296,10 +5300,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5322,19 +5326,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5383,7 +5387,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5398,7 +5402,7 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
@@ -5407,10 +5411,10 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5421,14 +5425,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5447,13 +5451,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5504,7 +5508,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5519,22 +5523,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5542,10 +5546,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5568,13 +5572,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5625,7 +5629,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5640,22 +5644,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5663,10 +5667,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5689,16 +5693,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5736,17 +5740,17 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5767,30 +5771,30 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5812,16 +5816,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5871,7 +5875,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5886,33 +5890,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5935,13 +5939,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5992,7 +5996,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6007,10 +6011,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -6019,10 +6023,10 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -6030,10 +6034,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6056,16 +6060,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6115,7 +6119,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6130,22 +6134,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>80</v>
@@ -6153,10 +6157,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6179,13 +6183,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6236,7 +6240,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6274,10 +6278,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6303,10 +6307,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6345,17 +6349,17 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6393,13 +6397,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6421,16 +6425,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6480,7 +6484,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6518,10 +6522,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6547,10 +6551,10 @@
         <v>93</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6601,7 +6605,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6610,7 +6614,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>80</v>
@@ -6628,7 +6632,7 @@
         <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6639,10 +6643,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6668,10 +6672,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6710,19 +6714,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6760,10 +6764,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6789,13 +6793,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6803,7 +6807,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6845,7 +6849,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6883,10 +6887,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6909,13 +6913,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6927,7 +6931,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6966,7 +6970,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6975,7 +6979,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7004,10 +7008,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7030,13 +7034,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7087,7 +7091,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7125,10 +7129,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7154,13 +7158,13 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7186,13 +7190,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7210,7 +7214,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7234,13 +7238,13 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7248,10 +7252,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7274,13 +7278,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7331,7 +7335,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7346,22 +7350,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7369,10 +7373,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7395,13 +7399,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7452,7 +7456,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7467,33 +7471,33 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7516,13 +7520,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7573,7 +7577,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7588,33 +7592,33 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7637,13 +7641,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7694,7 +7698,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7718,10 +7722,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7732,10 +7736,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7761,10 +7765,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7791,13 +7795,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7815,7 +7819,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7839,24 +7843,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7882,10 +7886,10 @@
         <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7912,13 +7916,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7936,7 +7940,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7960,24 +7964,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8000,13 +8004,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8057,7 +8061,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8072,19 +8076,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8095,10 +8099,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8121,13 +8125,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8178,7 +8182,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8205,7 +8209,7 @@
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -8216,10 +8220,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8248,7 +8252,7 @@
         <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -8289,19 +8293,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8328,7 +8332,7 @@
         <v>80</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8339,10 +8343,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8365,19 +8369,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8426,7 +8430,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8441,19 +8445,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8464,10 +8468,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8493,20 +8497,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8530,10 +8534,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8551,7 +8555,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8575,10 +8579,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8589,10 +8593,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8615,17 +8619,17 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8674,7 +8678,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8689,19 +8693,19 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8712,10 +8716,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8741,14 +8745,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8797,7 +8801,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8806,7 +8810,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8821,10 +8825,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8835,10 +8839,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8864,16 +8868,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8922,7 +8926,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8937,19 +8941,19 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8960,10 +8964,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8986,13 +8990,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9043,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9064,13 +9068,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9081,10 +9085,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9107,13 +9111,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9164,7 +9168,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9191,7 +9195,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9202,10 +9206,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9234,7 +9238,7 @@
         <v>138</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -9287,7 +9291,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9314,7 +9318,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9325,14 +9329,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9354,10 +9358,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9412,7 +9416,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9450,10 +9454,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9479,10 +9483,10 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9494,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>80</v>
@@ -9509,13 +9513,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9533,7 +9537,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9548,19 +9552,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9571,10 +9575,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9597,16 +9601,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9656,7 +9660,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9671,22 +9675,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9694,10 +9698,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9720,13 +9724,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9777,7 +9781,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9798,13 +9802,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9815,10 +9819,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9841,13 +9845,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9898,7 +9902,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9925,7 +9929,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9936,10 +9940,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9968,7 +9972,7 @@
         <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -10009,19 +10013,19 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10048,7 +10052,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10059,10 +10063,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10085,16 +10089,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10144,7 +10148,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10171,7 +10175,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10182,10 +10186,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10208,13 +10212,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10265,7 +10269,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10292,7 +10296,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10303,10 +10307,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10329,13 +10333,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10386,7 +10390,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10401,10 +10405,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10413,7 +10417,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10424,10 +10428,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10453,10 +10457,10 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10483,13 +10487,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10507,7 +10511,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10528,13 +10532,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10545,10 +10549,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10571,13 +10575,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10628,7 +10632,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10649,7 +10653,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10666,10 +10670,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10692,23 +10696,23 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10753,7 +10757,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10777,7 +10781,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10791,10 +10795,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10820,10 +10824,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10850,13 +10854,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10874,7 +10878,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10912,10 +10916,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10938,13 +10942,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10995,7 +10999,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11007,7 +11011,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -11033,10 +11037,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11059,13 +11063,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11116,7 +11120,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11143,7 +11147,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -11154,10 +11158,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11186,7 +11190,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -11239,7 +11243,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11266,7 +11270,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -11277,14 +11281,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11306,10 +11310,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11364,7 +11368,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11402,10 +11406,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11428,13 +11432,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11485,7 +11489,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11509,7 +11513,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11523,10 +11527,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11552,10 +11556,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11606,7 +11610,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11644,10 +11648,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11670,13 +11674,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11727,7 +11731,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11751,7 +11755,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11765,10 +11769,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11791,13 +11795,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11848,7 +11852,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11872,7 +11876,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11886,10 +11890,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11915,10 +11919,10 @@
         <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11945,13 +11949,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11969,7 +11973,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11993,7 +11997,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -12007,10 +12011,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12036,10 +12040,10 @@
         <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12066,13 +12070,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12090,7 +12094,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12128,10 +12132,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12154,16 +12158,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12213,7 +12217,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12237,10 +12241,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12251,10 +12255,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12277,13 +12281,13 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12334,7 +12338,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12361,7 +12365,7 @@
         <v>80</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>80</v>
@@ -12372,10 +12376,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12404,7 +12408,7 @@
         <v>138</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12457,7 +12461,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12484,7 +12488,7 @@
         <v>80</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12495,14 +12499,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12524,10 +12528,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12582,7 +12586,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12620,10 +12624,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12646,13 +12650,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12703,7 +12707,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12727,10 +12731,10 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12741,10 +12745,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12767,13 +12771,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12824,7 +12828,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12839,7 +12843,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12848,10 +12852,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12862,10 +12866,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12888,13 +12892,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12945,7 +12949,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12969,10 +12973,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12983,10 +12987,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13009,13 +13013,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13066,7 +13070,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13104,10 +13108,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13130,13 +13134,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13187,7 +13191,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13214,7 +13218,7 @@
         <v>80</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13225,10 +13229,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13257,7 +13261,7 @@
         <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>140</v>
@@ -13310,7 +13314,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13337,7 +13341,7 @@
         <v>80</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13348,14 +13352,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13377,10 +13381,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13435,7 +13439,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13473,10 +13477,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13499,13 +13503,13 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13556,7 +13560,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13594,10 +13598,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13620,13 +13624,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13677,7 +13681,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13715,10 +13719,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13744,10 +13748,10 @@
         <v>168</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13774,13 +13778,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13798,7 +13802,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13836,10 +13840,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13862,16 +13866,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13909,17 +13913,17 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13957,13 +13961,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13985,16 +13989,16 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14044,7 +14048,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14059,10 +14063,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14082,10 +14086,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14108,16 +14112,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14167,7 +14171,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -580,11 +580,10 @@
 </t>
   </si>
   <si>
-    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizationNameIEN
-Dim.ImmunizationName.CVXCode</t>
+    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - (9000010.11-.01 &gt; 9999999.14-) case 9999999.14-.03 not null</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationNameIEN</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -819,7 +818,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>332-1: undefined case not null</t>
+    <t>332-1: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case 9999999.14-.03 not null</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -5405,7 +5404,7 @@
         <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -580,10 +580,11 @@
 </t>
   </si>
   <si>
-    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - (9000010.11-.01 &gt; 9999999.14-) case 9999999.14-.03 not null</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizationNameIEN</t>
+    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationNameIEN
+Dim.ImmunizationName.CVXCode</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -818,7 +819,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>332-1: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case 9999999.14-.03 not null</t>
+    <t>332-1: undefined case not null</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -5404,7 +5405,7 @@
         <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,7 +552,7 @@
     <t>This is generally only used for the status of "not-done". The reason for performing the immunization event is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFimmunizationStatusReason</t>
+    <t>http://va.gov/fhir/ValueSet/immunizationStatusReason</t>
   </si>
   <si>
     <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
@@ -573,7 +573,7 @@
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX</t>
+    <t>http://va.gov/fhir/ValueSet/inferredCVX</t>
   </si>
   <si>
     <t xml:space="preserve">us-core-5
@@ -1083,7 +1083,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFimmunizationPrimarySource</t>
+    <t>http://va.gov/fhir/ConceptMap/immunizationPrimarySource</t>
   </si>
   <si>
     <t>Extension.value[x]</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -518,6 +518,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ImmunizationImmunization-297:if CVX populated then fixed value #completed {null}ImmunizationImmunization-299:if text like 'contraindicated', 'refused', 'decline', 'not avail' then fixed value #not-done {null}</t>
   </si>
   <si>
     <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
@@ -3802,25 +3806,25 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3828,10 +3832,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3854,16 +3858,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3893,7 +3897,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3911,7 +3915,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3926,19 +3930,19 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3949,10 +3953,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3975,13 +3979,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4012,7 +4016,7 @@
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4030,7 +4034,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -4039,39 +4043,39 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4094,13 +4098,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4151,7 +4155,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4178,7 +4182,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -4189,10 +4193,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4221,7 +4225,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -4262,19 +4266,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4301,7 +4305,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -4312,10 +4316,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4338,19 +4342,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4399,7 +4403,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4423,10 +4427,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4437,10 +4441,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4463,13 +4467,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4520,7 +4524,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4547,7 +4551,7 @@
         <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4558,10 +4562,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4590,7 +4594,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4631,19 +4635,19 @@
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4670,7 +4674,7 @@
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4681,10 +4685,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4710,16 +4714,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4729,7 +4733,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -4768,7 +4772,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4783,7 +4787,7 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
@@ -4792,10 +4796,10 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4806,10 +4810,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4832,16 +4836,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4891,7 +4895,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4915,10 +4919,10 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4929,10 +4933,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4958,14 +4962,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5014,7 +5018,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5029,19 +5033,19 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5052,10 +5056,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5078,17 +5082,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5137,7 +5141,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5161,10 +5165,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5175,10 +5179,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5201,19 +5205,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5262,7 +5266,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5286,10 +5290,10 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5300,10 +5304,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5326,19 +5330,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5387,7 +5391,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5402,7 +5406,7 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
@@ -5411,10 +5415,10 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5425,14 +5429,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5451,13 +5455,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5508,7 +5512,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5523,22 +5527,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5546,10 +5550,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5572,13 +5576,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5629,7 +5633,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5644,22 +5648,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>80</v>
@@ -5667,10 +5671,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5693,16 +5697,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5740,17 +5744,17 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5771,30 +5775,30 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5816,16 +5820,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5875,7 +5879,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5890,33 +5894,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5939,13 +5943,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5996,7 +6000,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6011,10 +6015,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -6023,10 +6027,10 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -6034,10 +6038,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6060,16 +6064,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6119,7 +6123,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6134,22 +6138,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>80</v>
@@ -6157,10 +6161,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6183,13 +6187,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6240,7 +6244,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6278,10 +6282,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6307,10 +6311,10 @@
         <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6349,17 +6353,17 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6397,13 +6401,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -6425,16 +6429,16 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6484,7 +6488,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6522,10 +6526,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6551,10 +6555,10 @@
         <v>93</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6605,7 +6609,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6614,7 +6618,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>80</v>
@@ -6632,7 +6636,7 @@
         <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6643,10 +6647,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6672,10 +6676,10 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6714,19 +6718,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6764,10 +6768,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6793,13 +6797,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6807,7 +6811,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -6849,7 +6853,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6887,10 +6891,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6913,13 +6917,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6931,7 +6935,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6970,7 +6974,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6979,7 +6983,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7008,10 +7012,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7034,13 +7038,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7091,7 +7095,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7129,10 +7133,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7155,16 +7159,16 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7190,13 +7194,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7214,7 +7218,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7238,13 +7242,13 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -7252,10 +7256,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7278,13 +7282,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7335,7 +7339,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7350,22 +7354,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7373,10 +7377,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7399,13 +7403,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7456,7 +7460,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7471,33 +7475,33 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7520,13 +7524,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7577,7 +7581,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7592,33 +7596,33 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7641,13 +7645,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7698,7 +7702,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7722,10 +7726,10 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7736,10 +7740,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7762,13 +7766,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7795,13 +7799,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7819,7 +7823,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7843,24 +7847,24 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7883,13 +7887,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7916,13 +7920,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7940,7 +7944,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7964,24 +7968,24 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8004,13 +8008,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8061,7 +8065,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8076,19 +8080,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8099,10 +8103,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8125,13 +8129,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8182,7 +8186,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8209,7 +8213,7 @@
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -8220,10 +8224,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8252,7 +8256,7 @@
         <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -8293,19 +8297,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8332,7 +8336,7 @@
         <v>80</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8343,10 +8347,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8369,19 +8373,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8430,7 +8434,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8445,19 +8449,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8468,10 +8472,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8497,20 +8501,20 @@
         <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>80</v>
@@ -8534,10 +8538,10 @@
         <v>160</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8555,7 +8559,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8579,10 +8583,10 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8593,10 +8597,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8619,17 +8623,17 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8678,7 +8682,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8693,19 +8697,19 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8716,10 +8720,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8745,14 +8749,14 @@
         <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8801,7 +8805,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8810,7 +8814,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8825,10 +8829,10 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8839,10 +8843,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8868,16 +8872,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8926,7 +8930,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8941,19 +8945,19 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8964,10 +8968,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8990,13 +8994,13 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9047,7 +9051,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9068,13 +9072,13 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9085,10 +9089,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9111,13 +9115,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9168,7 +9172,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9195,7 +9199,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9206,10 +9210,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9238,7 +9242,7 @@
         <v>138</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -9291,7 +9295,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9318,7 +9322,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9329,14 +9333,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9358,10 +9362,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -9416,7 +9420,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9454,10 +9458,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9480,13 +9484,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9498,7 +9502,7 @@
         <v>80</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>80</v>
@@ -9513,13 +9517,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9537,7 +9541,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9552,19 +9556,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9575,10 +9579,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9601,16 +9605,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9660,7 +9664,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>91</v>
@@ -9675,22 +9679,22 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9698,10 +9702,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9724,13 +9728,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9781,7 +9785,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9802,13 +9806,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9819,10 +9823,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9845,13 +9849,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9902,7 +9906,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9929,7 +9933,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9940,10 +9944,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9972,7 +9976,7 @@
         <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -10013,19 +10017,19 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10052,7 +10056,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -10063,10 +10067,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10089,16 +10093,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10148,7 +10152,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10175,7 +10179,7 @@
         <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -10186,10 +10190,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10212,13 +10216,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10269,7 +10273,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10296,7 +10300,7 @@
         <v>134</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -10307,10 +10311,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10333,13 +10337,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10390,7 +10394,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10405,10 +10409,10 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10417,7 +10421,7 @@
         <v>134</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10428,10 +10432,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10454,13 +10458,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10487,13 +10491,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10511,7 +10515,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10532,13 +10536,13 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10549,10 +10553,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10575,13 +10579,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10632,7 +10636,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10653,7 +10657,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10670,10 +10674,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10696,23 +10700,23 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>80</v>
@@ -10757,7 +10761,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10781,7 +10785,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>134</v>
@@ -10795,10 +10799,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10821,13 +10825,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10854,13 +10858,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10878,7 +10882,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10916,10 +10920,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10942,13 +10946,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10999,7 +11003,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11011,7 +11015,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -11037,10 +11041,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11063,13 +11067,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11120,7 +11124,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11147,7 +11151,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -11158,10 +11162,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11190,7 +11194,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -11243,7 +11247,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11270,7 +11274,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -11281,14 +11285,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11310,10 +11314,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11368,7 +11372,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11406,10 +11410,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11432,13 +11436,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11489,7 +11493,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11513,7 +11517,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>134</v>
@@ -11527,10 +11531,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11556,10 +11560,10 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11610,7 +11614,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11648,10 +11652,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11674,13 +11678,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11731,7 +11735,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11755,7 +11759,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>134</v>
@@ -11769,10 +11773,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11795,13 +11799,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11852,7 +11856,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11876,7 +11880,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>134</v>
@@ -11890,10 +11894,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11916,13 +11920,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11949,13 +11953,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11973,7 +11977,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11997,7 +12001,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>134</v>
@@ -12011,10 +12015,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12037,13 +12041,13 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12070,13 +12074,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12094,7 +12098,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12132,10 +12136,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12158,16 +12162,16 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12217,7 +12221,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12241,10 +12245,10 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -12255,10 +12259,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12281,13 +12285,13 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12338,7 +12342,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12365,7 +12369,7 @@
         <v>80</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>80</v>
@@ -12376,10 +12380,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12408,7 +12412,7 @@
         <v>138</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12461,7 +12465,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12488,7 +12492,7 @@
         <v>80</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>80</v>
@@ -12499,14 +12503,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12528,10 +12532,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12586,7 +12590,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12624,10 +12628,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12650,13 +12654,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12707,7 +12711,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12731,10 +12735,10 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -12745,10 +12749,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12771,13 +12775,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12828,7 +12832,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12843,7 +12847,7 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12852,10 +12856,10 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>80</v>
@@ -12866,10 +12870,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12892,13 +12896,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12949,7 +12953,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12973,10 +12977,10 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12987,10 +12991,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13013,13 +13017,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13070,7 +13074,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13108,10 +13112,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13134,13 +13138,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13191,7 +13195,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13218,7 +13222,7 @@
         <v>80</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
@@ -13229,10 +13233,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13261,7 +13265,7 @@
         <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>140</v>
@@ -13314,7 +13318,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13341,7 +13345,7 @@
         <v>80</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13352,14 +13356,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13381,10 +13385,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13439,7 +13443,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13477,10 +13481,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13503,13 +13507,13 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13560,7 +13564,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13598,10 +13602,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13624,13 +13628,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13681,7 +13685,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13719,10 +13723,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13745,13 +13749,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13778,13 +13782,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13802,7 +13806,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13840,10 +13844,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13866,16 +13870,16 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13913,17 +13917,17 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13961,13 +13965,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13989,16 +13993,16 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14048,7 +14052,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>91</v>
@@ -14063,10 +14067,10 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
@@ -14086,10 +14090,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14112,16 +14116,16 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14171,7 +14175,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -521,7 +521,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ImmunizationImmunization-297:if CVX populated then fixed value #completed {null}ImmunizationImmunization-299:if text like 'contraindicated', 'refused', 'decline', 'not avail' then fixed value #not-done {null}</t>
+ii-24-297:9000010.11-.01 &gt; 9999999.14-.03: if CVX populated then #completed {null}ii-24-299:9000010.11-.01 &gt; 9999999.14-.01: if text like 'contraindicated', 'refused', 'decline', 'not avail' then #not-done {null}</t>
   </si>
   <si>
     <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1163,6 +1163,10 @@
   <si>
     <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN
 Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
+  </si>
+  <si>
+    <t>immunization.administered,immunization.encounter,immunization.facility,immunization.location
+visit.creditStopCode,visit.location,visit.service,visit.visitString</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -7505,19 +7509,19 @@
         <v>369</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>282</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7525,10 +7529,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7551,13 +7555,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7608,7 +7612,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7623,10 +7627,10 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -7635,24 +7639,24 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7678,10 +7682,10 @@
         <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7732,7 +7736,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7747,10 +7751,10 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7759,24 +7763,24 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7799,13 +7803,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7856,7 +7860,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7883,10 +7887,10 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7897,10 +7901,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7926,10 +7930,10 @@
         <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7959,10 +7963,10 @@
         <v>360</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7980,7 +7984,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8007,24 +8011,24 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8050,10 +8054,10 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8083,10 +8087,10 @@
         <v>360</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -8104,7 +8108,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8131,24 +8135,24 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8171,13 +8175,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8228,7 +8232,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8243,10 +8247,10 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -8255,10 +8259,10 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
@@ -8269,10 +8273,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8393,10 +8397,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8519,10 +8523,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8545,19 +8549,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8606,7 +8610,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8621,22 +8625,22 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8647,10 +8651,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8676,20 +8680,20 @@
         <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>81</v>
@@ -8713,10 +8717,10 @@
         <v>161</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8734,7 +8738,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8761,10 +8765,10 @@
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8775,10 +8779,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8804,14 +8808,14 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8860,7 +8864,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8875,10 +8879,10 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -8887,10 +8891,10 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>81</v>
@@ -8901,10 +8905,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8930,14 +8934,14 @@
         <v>106</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8986,7 +8990,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8995,7 +8999,7 @@
         <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -9013,10 +9017,10 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -9027,10 +9031,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9056,16 +9060,16 @@
         <v>112</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -9114,7 +9118,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9129,10 +9133,10 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -9141,10 +9145,10 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -9155,10 +9159,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9181,13 +9185,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9238,7 +9242,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9262,13 +9266,13 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -9279,10 +9283,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9403,10 +9407,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9529,14 +9533,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9558,10 +9562,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>141</v>
@@ -9616,7 +9620,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9657,10 +9661,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9686,10 +9690,10 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9701,7 +9705,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9716,13 +9720,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9740,7 +9744,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9755,7 +9759,7 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9764,13 +9768,13 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9781,10 +9785,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9807,16 +9811,16 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9866,7 +9870,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>92</v>
@@ -9881,25 +9885,25 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9907,10 +9911,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9933,13 +9937,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9990,7 +9994,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10014,13 +10018,13 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>
@@ -10031,10 +10035,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10155,10 +10159,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10281,10 +10285,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10307,16 +10311,16 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10366,7 +10370,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10396,7 +10400,7 @@
         <v>135</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10407,10 +10411,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10436,10 +10440,10 @@
         <v>300</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10490,7 +10494,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10520,7 +10524,7 @@
         <v>135</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10531,10 +10535,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10557,13 +10561,13 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10614,7 +10618,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>92</v>
@@ -10629,13 +10633,13 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10644,7 +10648,7 @@
         <v>135</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
@@ -10655,10 +10659,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10684,10 +10688,10 @@
         <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10717,10 +10721,10 @@
         <v>360</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10738,7 +10742,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10762,13 +10766,13 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>81</v>
@@ -10779,10 +10783,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10805,13 +10809,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10862,7 +10866,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10886,7 +10890,7 @@
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10903,10 +10907,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10932,20 +10936,20 @@
         <v>248</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>81</v>
@@ -10990,7 +10994,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11017,7 +11021,7 @@
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>135</v>
@@ -11031,10 +11035,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11060,10 +11064,10 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11093,10 +11097,10 @@
         <v>360</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -11114,7 +11118,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11155,10 +11159,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11181,13 +11185,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11238,7 +11242,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11250,7 +11254,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -11279,10 +11283,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11403,10 +11407,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11529,14 +11533,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11558,10 +11562,10 @@
         <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>141</v>
@@ -11616,7 +11620,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11657,10 +11661,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11686,10 +11690,10 @@
         <v>192</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11740,7 +11744,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11767,7 +11771,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>135</v>
@@ -11781,10 +11785,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11810,10 +11814,10 @@
         <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11864,7 +11868,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11905,10 +11909,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11934,10 +11938,10 @@
         <v>300</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11988,7 +11992,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12015,7 +12019,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>135</v>
@@ -12029,10 +12033,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12058,10 +12062,10 @@
         <v>300</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12112,7 +12116,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12139,7 +12143,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>135</v>
@@ -12153,10 +12157,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12182,10 +12186,10 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12215,10 +12219,10 @@
         <v>360</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -12236,7 +12240,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12263,7 +12267,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>135</v>
@@ -12277,10 +12281,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12306,10 +12310,10 @@
         <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12339,10 +12343,10 @@
         <v>360</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -12360,7 +12364,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12401,10 +12405,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12427,16 +12431,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12486,7 +12490,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12513,10 +12517,10 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>81</v>
@@ -12527,10 +12531,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12651,10 +12655,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12777,14 +12781,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12806,10 +12810,10 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>141</v>
@@ -12864,7 +12868,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -12905,10 +12909,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12934,10 +12938,10 @@
         <v>300</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12988,7 +12992,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13015,7 +13019,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>295</v>
@@ -13029,10 +13033,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13055,13 +13059,13 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13112,7 +13116,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13127,7 +13131,7 @@
         <v>104</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -13139,10 +13143,10 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>81</v>
@@ -13153,10 +13157,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13182,10 +13186,10 @@
         <v>248</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13236,7 +13240,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13263,10 +13267,10 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>81</v>
@@ -13277,10 +13281,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13303,13 +13307,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13360,7 +13364,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13401,10 +13405,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13525,10 +13529,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13651,14 +13655,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13680,10 +13684,10 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>141</v>
@@ -13738,7 +13742,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13779,10 +13783,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13808,10 +13812,10 @@
         <v>192</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13862,7 +13866,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -13903,10 +13907,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13929,13 +13933,13 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13986,7 +13990,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14027,10 +14031,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14056,10 +14060,10 @@
         <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14089,10 +14093,10 @@
         <v>360</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -14110,7 +14114,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14151,10 +14155,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14177,16 +14181,16 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14234,7 +14238,7 @@
         <v>201</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>92</v>
@@ -14275,13 +14279,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>81</v>
@@ -14306,13 +14310,13 @@
         <v>192</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14362,7 +14366,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>92</v>
@@ -14377,13 +14381,13 @@
         <v>104</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -14403,10 +14407,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14429,16 +14433,16 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14488,7 +14492,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="650">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -534,7 +534,8 @@
 Dim.ImmunizationName.ImmunizationName,Dim.PharmacyOrderableItem.ImmunizationName</t>
   </si>
   <si>
-    <t>immunization.cvx,immunization.name</t>
+    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.VaccinationExtension.CDCName,Vaccination.VaccinationExtension.Source,Vaccination.AdministrationSite.Description,Vaccination.VA.Manufacturer.Description
+Vaccination.Order.Description,Vaccination.Route.Description,Vaccination.Order.Description,Vaccination.ObservationValueCode.Description</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -597,6 +598,10 @@
 Dim.ImmunizationName.CVXCode</t>
   </si>
   <si>
+    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.VaccinationExtension.CDCName,Vaccination.VaccinationExtension.Source,Vaccination.AdministrationSite.Description,Vaccination.VA.Manufacturer.Description
+Vaccination.Order.Code,Vaccination.Route.Code,Vaccination.Order.Code</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -861,6 +866,9 @@
     <t>Immun.Immunization.PatientIEN</t>
   </si>
   <si>
+    <t>Vaccination.AdministrationSite.Code,Vaccination.VA.Manufacturer.Code</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -892,7 +900,7 @@
     <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN</t>
   </si>
   <si>
-    <t>immunization.administered,immunization.encounter,immunization.facility,immunization.location</t>
+    <t>Vaccination.EncounterNumber,Vaccination.EnteredAt,Vaccination.Administration.AdministeredAtLocation</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -958,6 +966,9 @@
     <t>Immun.Immunization.EventDateTime</t>
   </si>
   <si>
+    <t>Vaccination.FromTime,Vaccination.ToTime</t>
+  </si>
+  <si>
     <t>Immunization.recorded</t>
   </si>
   <si>
@@ -997,7 +1008,7 @@
     <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
   </si>
   <si>
-    <t>immunization.source</t>
+    <t>Vaccination.VaccinationExtension.Source</t>
   </si>
   <si>
     <t>RXA-9</t>
@@ -1165,8 +1176,8 @@
 Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
   </si>
   <si>
-    <t>immunization.administered,immunization.encounter,immunization.facility,immunization.location
-visit.creditStopCode,visit.location,visit.service,visit.visitString</t>
+    <t>Vaccination.EncounterNumber,Vaccination.EnteredAt,Vaccination.Administration.AdministeredAtLocation
+Encounter.ExternalId,Encounter.HealthCareFacility</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -1319,6 +1330,9 @@
     <t>Immun.Immunization.DoseUnit</t>
   </si>
   <si>
+    <t>Vaccination.Administration.AdministeredUnits</t>
+  </si>
+  <si>
     <t>RXA-6 / RXA-7</t>
   </si>
   <si>
@@ -1359,7 +1373,7 @@
     <t>Immun.Immunization.Dosage</t>
   </si>
   <si>
-    <t>immunization.dose</t>
+    <t>Vaccination.Administration.AdministeredAmount</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -1578,7 +1592,7 @@
     <t>Immun.Immunization.ImmunizingStaffIEN</t>
   </si>
   <si>
-    <t>immunization.provider</t>
+    <t>Vaccination.Administration.AdministeringProvider</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1677,7 +1691,7 @@
     <t>Immun.Immunization.ImmunizationComments</t>
   </si>
   <si>
-    <t>immunization.comment</t>
+    <t>Vaccination.Comments</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -2005,7 +2019,7 @@
     <t>Immun.Immunization.Series</t>
   </si>
   <si>
-    <t>immunization.series</t>
+    <t>Vaccination.Administration.AdministrationStatus</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -2371,7 +2385,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="189.8125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.1015625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="90.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="208.11328125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="147.5546875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="236.8828125" customWidth="true" bestFit="true"/>
@@ -4123,30 +4137,30 @@
         <v>185</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4169,13 +4183,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4226,7 +4240,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4256,7 +4270,7 @@
         <v>81</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -4267,10 +4281,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4299,7 +4313,7 @@
         <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>141</v>
@@ -4340,19 +4354,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4382,7 +4396,7 @@
         <v>81</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>81</v>
@@ -4393,10 +4407,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4419,19 +4433,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4480,7 +4494,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4507,10 +4521,10 @@
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -4521,10 +4535,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4547,13 +4561,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4604,7 +4618,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4634,7 +4648,7 @@
         <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4645,10 +4659,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4677,7 +4691,7 @@
         <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>141</v>
@@ -4718,19 +4732,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4760,7 +4774,7 @@
         <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4771,10 +4785,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4800,16 +4814,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4819,7 +4833,7 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>81</v>
@@ -4858,7 +4872,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4873,7 +4887,7 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4885,10 +4899,10 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4899,10 +4913,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4925,16 +4939,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4984,7 +4998,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5011,10 +5025,10 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>81</v>
@@ -5025,10 +5039,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5054,14 +5068,14 @@
         <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -5110,7 +5124,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5125,10 +5139,10 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -5137,10 +5151,10 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>81</v>
@@ -5151,10 +5165,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5177,17 +5191,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5236,7 +5250,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5263,10 +5277,10 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>81</v>
@@ -5277,10 +5291,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5303,19 +5317,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5364,7 +5378,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5391,10 +5405,10 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>81</v>
@@ -5405,10 +5419,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5431,19 +5445,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5492,7 +5506,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5507,7 +5521,7 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
@@ -5519,10 +5533,10 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>81</v>
@@ -5533,14 +5547,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5559,13 +5573,13 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5616,7 +5630,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5631,25 +5645,25 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -5657,10 +5671,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5683,13 +5697,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5740,7 +5754,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5755,25 +5769,25 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -5781,10 +5795,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5807,16 +5821,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5854,17 +5868,17 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5888,30 +5902,30 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>81</v>
@@ -5933,16 +5947,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5992,7 +6006,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>92</v>
@@ -6007,36 +6021,36 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6059,13 +6073,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6116,7 +6130,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6131,10 +6145,10 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
@@ -6146,10 +6160,10 @@
         <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -6157,10 +6171,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6183,16 +6197,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6242,7 +6256,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6257,25 +6271,25 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -6283,10 +6297,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6309,13 +6323,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6366,7 +6380,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6407,10 +6421,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6436,10 +6450,10 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6478,17 +6492,17 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6529,13 +6543,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="C34" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>81</v>
@@ -6557,16 +6571,16 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6616,7 +6630,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6657,10 +6671,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6686,10 +6700,10 @@
         <v>94</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6740,7 +6754,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6749,7 +6763,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>81</v>
@@ -6770,7 +6784,7 @@
         <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6781,10 +6795,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6810,10 +6824,10 @@
         <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6852,19 +6866,19 @@
         <v>81</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6905,10 +6919,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6934,13 +6948,13 @@
         <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6948,7 +6962,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>81</v>
@@ -6990,7 +7004,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>92</v>
@@ -7031,10 +7045,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7057,13 +7071,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7075,7 +7089,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -7114,7 +7128,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7123,7 +7137,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -7155,10 +7169,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7181,13 +7195,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7238,7 +7252,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7279,10 +7293,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7308,13 +7322,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7340,13 +7354,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7364,7 +7378,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7391,13 +7405,13 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7405,10 +7419,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7431,13 +7445,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7488,7 +7502,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7503,25 +7517,25 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7529,10 +7543,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7555,13 +7569,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7612,7 +7626,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7627,10 +7641,10 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -7639,24 +7653,24 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7679,13 +7693,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7736,7 +7750,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7751,10 +7765,10 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7763,24 +7777,24 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7803,13 +7817,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7860,7 +7874,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7887,10 +7901,10 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7901,10 +7915,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7930,10 +7944,10 @@
         <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7960,31 +7974,31 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8011,24 +8025,24 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8054,10 +8068,10 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8084,31 +8098,31 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8135,24 +8149,24 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8175,13 +8189,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8232,7 +8246,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8247,22 +8261,22 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
@@ -8273,10 +8287,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8299,13 +8313,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8356,7 +8370,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8386,7 +8400,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8397,10 +8411,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8429,7 +8443,7 @@
         <v>139</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>141</v>
@@ -8470,19 +8484,19 @@
         <v>81</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8512,7 +8526,7 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8523,10 +8537,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8549,19 +8563,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8610,7 +8624,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8625,22 +8639,22 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8651,10 +8665,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8680,20 +8694,20 @@
         <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>81</v>
@@ -8717,10 +8731,10 @@
         <v>161</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8738,7 +8752,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8765,10 +8779,10 @@
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8779,10 +8793,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8805,17 +8819,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8864,7 +8878,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8879,22 +8893,22 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>81</v>
@@ -8905,10 +8919,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8934,14 +8948,14 @@
         <v>106</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8990,7 +9004,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8999,7 +9013,7 @@
         <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -9017,10 +9031,10 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -9031,10 +9045,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9060,16 +9074,16 @@
         <v>112</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -9118,7 +9132,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9133,22 +9147,22 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -9159,10 +9173,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9185,13 +9199,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9242,7 +9256,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9266,13 +9280,13 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -9283,10 +9297,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9309,13 +9323,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9366,7 +9380,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9396,7 +9410,7 @@
         <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9407,10 +9421,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9439,7 +9453,7 @@
         <v>139</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>141</v>
@@ -9492,7 +9506,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9522,7 +9536,7 @@
         <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9533,14 +9547,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9562,10 +9576,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>141</v>
@@ -9620,7 +9634,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9661,10 +9675,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9690,10 +9704,10 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9705,7 +9719,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9720,31 +9734,31 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9759,7 +9773,7 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9768,13 +9782,13 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9785,10 +9799,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9811,16 +9825,16 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9870,7 +9884,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>92</v>
@@ -9885,25 +9899,25 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9911,10 +9925,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9937,13 +9951,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9994,7 +10008,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10018,13 +10032,13 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>
@@ -10035,10 +10049,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10061,13 +10075,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10118,7 +10132,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10148,7 +10162,7 @@
         <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>
@@ -10159,10 +10173,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10191,7 +10205,7 @@
         <v>139</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>141</v>
@@ -10232,19 +10246,19 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10274,7 +10288,7 @@
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>81</v>
@@ -10285,10 +10299,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10311,16 +10325,16 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10370,7 +10384,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10400,7 +10414,7 @@
         <v>135</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10411,10 +10425,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10437,13 +10451,13 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10494,7 +10508,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10524,7 +10538,7 @@
         <v>135</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10535,10 +10549,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10561,13 +10575,13 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10618,7 +10632,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>92</v>
@@ -10633,13 +10647,13 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10648,7 +10662,7 @@
         <v>135</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
@@ -10659,10 +10673,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10688,10 +10702,10 @@
         <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10718,31 +10732,31 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="Z67" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10766,13 +10780,13 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>81</v>
@@ -10783,10 +10797,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10809,13 +10823,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10866,7 +10880,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10890,7 +10904,7 @@
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10907,10 +10921,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10933,68 +10947,68 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q69" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="R69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="R69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11021,7 +11035,7 @@
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>135</v>
@@ -11035,10 +11049,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11064,10 +11078,10 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11094,31 +11108,31 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="Z70" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11159,10 +11173,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11185,13 +11199,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11242,7 +11256,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11254,7 +11268,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -11283,10 +11297,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11309,13 +11323,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11366,7 +11380,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11396,7 +11410,7 @@
         <v>81</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>81</v>
@@ -11407,10 +11421,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11439,7 +11453,7 @@
         <v>139</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>141</v>
@@ -11492,7 +11506,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11522,7 +11536,7 @@
         <v>81</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>81</v>
@@ -11533,14 +11547,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11562,10 +11576,10 @@
         <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>141</v>
@@ -11620,7 +11634,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11661,10 +11675,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11687,13 +11701,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11744,7 +11758,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11771,7 +11785,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>135</v>
@@ -11785,10 +11799,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11814,10 +11828,10 @@
         <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11868,7 +11882,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11909,10 +11923,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11935,13 +11949,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11992,7 +12006,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12019,7 +12033,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>135</v>
@@ -12033,10 +12047,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12059,13 +12073,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12116,7 +12130,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12143,7 +12157,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>135</v>
@@ -12157,10 +12171,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12186,10 +12200,10 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12216,31 +12230,31 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="Z79" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12267,7 +12281,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>135</v>
@@ -12281,10 +12295,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12310,10 +12324,10 @@
         <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12340,31 +12354,31 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="Z80" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12405,10 +12419,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12431,16 +12445,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12490,7 +12504,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12517,10 +12531,10 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>81</v>
@@ -12531,10 +12545,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12557,13 +12571,13 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12614,7 +12628,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12644,7 +12658,7 @@
         <v>81</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>81</v>
@@ -12655,10 +12669,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12687,7 +12701,7 @@
         <v>139</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>141</v>
@@ -12740,7 +12754,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12770,7 +12784,7 @@
         <v>81</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>81</v>
@@ -12781,14 +12795,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12810,10 +12824,10 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>141</v>
@@ -12868,7 +12882,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -12909,10 +12923,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12935,13 +12949,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12992,7 +13006,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13019,10 +13033,10 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>81</v>
@@ -13033,10 +13047,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13059,13 +13073,13 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13116,7 +13130,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13131,7 +13145,7 @@
         <v>104</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -13143,10 +13157,10 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>81</v>
@@ -13157,10 +13171,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13183,13 +13197,13 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13240,7 +13254,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13267,10 +13281,10 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>81</v>
@@ -13281,10 +13295,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13307,13 +13321,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13364,7 +13378,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13405,10 +13419,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13431,13 +13445,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13488,7 +13502,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13518,7 +13532,7 @@
         <v>81</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>81</v>
@@ -13529,10 +13543,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13561,7 +13575,7 @@
         <v>139</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>141</v>
@@ -13614,7 +13628,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13644,7 +13658,7 @@
         <v>81</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>81</v>
@@ -13655,14 +13669,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13684,10 +13698,10 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>141</v>
@@ -13742,7 +13756,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13783,10 +13797,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13809,13 +13823,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13866,7 +13880,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -13907,10 +13921,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13933,13 +13947,13 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13990,7 +14004,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14031,10 +14045,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14060,10 +14074,10 @@
         <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14090,31 +14104,31 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="Z94" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14155,10 +14169,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14181,16 +14195,16 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14228,17 +14242,17 @@
         <v>81</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>92</v>
@@ -14279,13 +14293,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>81</v>
@@ -14307,16 +14321,16 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14366,7 +14380,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>92</v>
@@ -14381,13 +14395,13 @@
         <v>104</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -14407,10 +14421,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14433,16 +14447,16 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14492,7 +14506,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -534,8 +534,8 @@
 Dim.ImmunizationName.ImmunizationName,Dim.PharmacyOrderableItem.ImmunizationName</t>
   </si>
   <si>
-    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.VaccinationExtension.CDCName,Vaccination.VaccinationExtension.Source,Vaccination.AdministrationSite.Description,Vaccination.VA.Manufacturer.Description
-Vaccination.Order.Description,Vaccination.Route.Description,Vaccination.Order.Description,Vaccination.ObservationValueCode.Description</t>
+    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.Extension[VaccinationExtension].CDCName,Vaccination.Extension[VaccinationExtension].Source,Vaccination.AdministrationSite.Description,Vaccination.Manufacturer[VA.Manufacturer].Description
+Vaccination.OrderItem[Order].Description,Vaccination.Route.Description,Vaccination.OrderItem[Order].Description,Vaccination.ObservationCodedValue[ObservationValueCode].Description</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -598,8 +598,8 @@
 Dim.ImmunizationName.CVXCode</t>
   </si>
   <si>
-    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.VaccinationExtension.CDCName,Vaccination.VaccinationExtension.Source,Vaccination.AdministrationSite.Description,Vaccination.VA.Manufacturer.Description
-Vaccination.Order.Code,Vaccination.Route.Code,Vaccination.Order.Code</t>
+    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.Extension[VaccinationExtension].CDCName,Vaccination.Extension[VaccinationExtension].Source,Vaccination.AdministrationSite.Description,Vaccination.Manufacturer[VA.Manufacturer].Description
+Vaccination.OrderItem[Order].Code,Vaccination.Route.Code,Vaccination.OrderItem[Order].Code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -866,7 +866,7 @@
     <t>Immun.Immunization.PatientIEN</t>
   </si>
   <si>
-    <t>Vaccination.AdministrationSite.Code,Vaccination.VA.Manufacturer.Code</t>
+    <t>Vaccination.AdministrationSite.Code,Vaccination.Manufacturer[VA.Manufacturer].Code</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1008,7 +1008,7 @@
     <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
   </si>
   <si>
-    <t>Vaccination.VaccinationExtension.Source</t>
+    <t>Vaccination.Extension[VaccinationExtension].Source</t>
   </si>
   <si>
     <t>RXA-9</t>
@@ -2385,7 +2385,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="189.8125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.1015625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="208.11328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="242.7265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="147.5546875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="236.8828125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (9000010.11) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (9000010.11) to us-core-immunization.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1110,7 +1110,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/immunizationPrimarySource</t>
+    <t>http://va.gov/fhir/ConceptMap/VF-immunizationPrimarySource</t>
   </si>
   <si>
     <t>Extension.value[x]</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -524,10 +524,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-297:9000010.11-.01 &gt; 9999999.14-.03: if CVX populated then #completed {null}ii-24-299:9000010.11-.01 &gt; 9999999.14-.01: if text like 'contraindicated', 'refused', 'decline', 'not avail' then #not-done {null}</t>
-  </si>
-  <si>
-    <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
+ii-24-297:If (9000010.11-.01 &gt; 9999999.14-.03) is CVX populated then fixed value #completed {null}ii-24-298:If (9000010.11-.01 &gt; 9999999.14-.01) is missing or unknown then exclude record {null}ii-24-299:If (9000010.11-.01 &gt; 9999999.14-.01) is text like 'contraindicated', 'refused', 'decline', 'not avail' then fixed value #not-done {null}</t>
+  </si>
+  <si>
+    <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationNameIEN
@@ -566,7 +566,11 @@
     <t>http://va.gov/fhir/ValueSet/immunizationStatusReason</t>
   </si>
   <si>
-    <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) case V IMMUNIZATION - IMMUNIZATION null</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ii-24-527:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_immunizationStatusReason {null}</t>
+  </si>
+  <si>
+    <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if V IMMUNIZATION - IMMUNIZATION null</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -591,7 +595,11 @@
 </t>
   </si>
   <si>
-    <t>332: source value from V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) case not null</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ii-24-528:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_inferredCVX {null}ii-24-332:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03) {null}</t>
+  </si>
+  <si>
+    <t>332: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) if not null</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationNameIEN
@@ -755,7 +763,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1609: source value from V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
+    <t>1609: source value based on V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.NDCCodeVAText</t>
@@ -834,7 +842,11 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>332-1: undefined case not null</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ii-24-332-1:If not null then source value from (undefined) {null}</t>
+  </si>
+  <si>
+    <t>332-1: source value if not null</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -860,7 +872,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>333: source value from V IMMUNIZATION - PATIENT NAME (9000010.11-.02)</t>
+    <t>333: source value based on V IMMUNIZATION - PATIENT NAME (9000010.11-.02)</t>
   </si>
   <si>
     <t>Immun.Immunization.PatientIEN</t>
@@ -894,7 +906,7 @@
     <t>The visit or admission or other contact between patient and health care provider the immunization was performed as part of.</t>
   </si>
   <si>
-    <t>1767: reference from V IMMUNIZATION - VISIT (9000010.11-.03)</t>
+    <t>1767: reference based on V IMMUNIZATION - VISIT (9000010.11-.03)</t>
   </si>
   <si>
     <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN</t>
@@ -960,7 +972,7 @@
 </t>
   </si>
   <si>
-    <t>334: source value from V IMMUNIZATION - EVENT DATE AND TIME (9000010.11-1201)</t>
+    <t>334: source value based on V IMMUNIZATION - EVENT DATE AND TIME (9000010.11-1201)</t>
   </si>
   <si>
     <t>Immun.Immunization.EventDateTime</t>
@@ -978,7 +990,7 @@
     <t>The date the occurrence of the immunization was first captured in the record - potentially significantly after the occurrence of the event.</t>
   </si>
   <si>
-    <t>1593: source value from V IMMUNIZATION - DATE/TIME RECORDED (9000010.11-1205)</t>
+    <t>1593: source value based on V IMMUNIZATION - DATE/TIME RECORDED (9000010.11-1205)</t>
   </si>
   <si>
     <t>Immun.Immunization.RecordedDateTime</t>
@@ -1169,7 +1181,7 @@
     <t>The service delivery location where the vaccine administration occurred.</t>
   </si>
   <si>
-    <t>1801: reference from V IMMUNIZATION - VISIT &gt; VISIT - HOSPITAL LOCATION (9000010.11-.03 &gt; 9000010-.22)</t>
+    <t>1801: reference based on V IMMUNIZATION - VISIT &gt; VISIT - HOSPITAL LOCATION (9000010.11-.03 &gt; 9000010-.22)</t>
   </si>
   <si>
     <t>Immun.Immunization.OutsideLocation,Immun.Immunization.VisitDateTime,Immun.Immunization.VisitIEN
@@ -1205,7 +1217,7 @@
     <t>Name of vaccine manufacturer.</t>
   </si>
   <si>
-    <t>339: source value from V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - MANUFACTURER (9000010.11-.05 &gt; 9999999.41-.02)</t>
+    <t>339: source value based on V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - MANUFACTURER (9000010.11-.05 &gt; 9999999.41-.02)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.ImmunizationManufacturerIEN,Dim.ImmunizationLot.ImmunizationManufacturerSID</t>
@@ -1229,7 +1241,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>338: source value from V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - LOT NUMBER (9000010.11-.05 &gt; 9999999.41-.01)</t>
+    <t>338: source value based on V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - LOT NUMBER (9000010.11-.05 &gt; 9999999.41-.01)</t>
   </si>
   <si>
     <t>Dim.ImmunizationLot.ImmunizationLot</t>
@@ -1324,7 +1336,7 @@
     <t>The quantity of vaccine product that was administered.</t>
   </si>
   <si>
-    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (9000010.11-1313 &gt; 757.5-)</t>
+    <t>464: source value based on V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (9000010.11-1313 &gt; 757.5-)</t>
   </si>
   <si>
     <t>Immun.Immunization.DoseUnit</t>
@@ -1367,7 +1379,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>340: source value from V IMMUNIZATION - DOSE (9000010.11-1312)</t>
+    <t>340: source value based on V IMMUNIZATION - DOSE (9000010.11-1312)</t>
   </si>
   <si>
     <t>Immun.Immunization.Dosage</t>
@@ -1427,7 +1439,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>464-1: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - DESCRIPTION OF THE UNIT (9000010.11-1313 &gt; 757.5-.01)</t>
+    <t>464-1: source value based on V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - DESCRIPTION OF THE UNIT (9000010.11-1313 &gt; 757.5-.01)</t>
   </si>
   <si>
     <t>Immun.Immunization.DoseUnit
@@ -1480,7 +1492,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>464-2: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - UCUM CODE (9000010.11-1313 &gt; 757.5-1)</t>
+    <t>464-2: source value based on V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - UCUM CODE (9000010.11-1313 &gt; 757.5-1)</t>
   </si>
   <si>
     <t>Immun.Immunization.DoseUnit
@@ -1586,7 +1598,7 @@
     <t>When the individual practitioner who performed the action is known, it is best to send.</t>
   </si>
   <si>
-    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (9000010.11-1204)</t>
+    <t>342: reference based on V IMMUNIZATION - ENCOUNTER PROVIDER (9000010.11-1204)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizingStaffIEN</t>
@@ -1685,7 +1697,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>343: source value from V IMMUNIZATION - COMMENTS (9000010.11-81101)</t>
+    <t>343: source value based on V IMMUNIZATION - COMMENTS (9000010.11-81101)</t>
   </si>
   <si>
     <t>Immun.Immunization.ImmunizationComments</t>
@@ -2013,7 +2025,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>344: source value from V IMMUNIZATION - SERIES (9000010.11-.04)</t>
+    <t>344: source value based on V IMMUNIZATION - SERIES (9000010.11-.04)</t>
   </si>
   <si>
     <t>Immun.Immunization.Series</t>
@@ -2383,7 +2395,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="189.8125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="186.75390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.1015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="242.7265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -4006,10 +4018,10 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>165</v>
@@ -4018,13 +4030,13 @@
         <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>81</v>
@@ -4035,10 +4047,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4064,10 +4076,10 @@
         <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4098,7 +4110,7 @@
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4116,7 +4128,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>92</v>
@@ -4125,42 +4137,42 @@
         <v>92</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4183,13 +4195,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4240,7 +4252,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4270,7 +4282,7 @@
         <v>81</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -4281,10 +4293,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4313,7 +4325,7 @@
         <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>141</v>
@@ -4354,19 +4366,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4396,7 +4408,7 @@
         <v>81</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>81</v>
@@ -4407,10 +4419,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4433,19 +4445,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4494,7 +4506,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4521,10 +4533,10 @@
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -4535,10 +4547,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4561,13 +4573,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4618,7 +4630,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4648,7 +4660,7 @@
         <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4659,10 +4671,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4691,7 +4703,7 @@
         <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>141</v>
@@ -4732,19 +4744,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4774,7 +4786,7 @@
         <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4785,10 +4797,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4814,16 +4826,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4833,7 +4845,7 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>81</v>
@@ -4872,7 +4884,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4887,7 +4899,7 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4899,10 +4911,10 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4913,10 +4925,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4939,16 +4951,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4998,7 +5010,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5025,10 +5037,10 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>81</v>
@@ -5039,10 +5051,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5068,14 +5080,14 @@
         <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -5124,7 +5136,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5139,10 +5151,10 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -5151,10 +5163,10 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>81</v>
@@ -5165,10 +5177,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5191,17 +5203,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5250,7 +5262,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5277,10 +5289,10 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>81</v>
@@ -5291,10 +5303,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5317,19 +5329,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5378,7 +5390,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5405,10 +5417,10 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>81</v>
@@ -5419,10 +5431,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5445,19 +5457,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5506,7 +5518,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5518,10 +5530,10 @@
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
@@ -5533,10 +5545,10 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>81</v>
@@ -5547,14 +5559,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5573,13 +5585,13 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5630,7 +5642,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5645,25 +5657,25 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -5671,10 +5683,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5697,13 +5709,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5754,7 +5766,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5769,25 +5781,25 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -5795,10 +5807,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5821,16 +5833,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5868,17 +5880,17 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5902,30 +5914,30 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>81</v>
@@ -5947,16 +5959,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6006,7 +6018,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>92</v>
@@ -6021,36 +6033,36 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6073,13 +6085,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6130,7 +6142,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6145,10 +6157,10 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
@@ -6160,10 +6172,10 @@
         <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -6171,10 +6183,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6197,16 +6209,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6256,7 +6268,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6271,25 +6283,25 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -6297,10 +6309,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6323,13 +6335,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6380,7 +6392,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6421,10 +6433,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6450,10 +6462,10 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6492,17 +6504,17 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6543,13 +6555,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="C34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>81</v>
@@ -6571,16 +6583,16 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6630,7 +6642,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6671,10 +6683,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6700,10 +6712,10 @@
         <v>94</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6754,7 +6766,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6763,7 +6775,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>81</v>
@@ -6784,7 +6796,7 @@
         <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6795,10 +6807,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6824,10 +6836,10 @@
         <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6866,19 +6878,19 @@
         <v>81</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6919,10 +6931,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6948,13 +6960,13 @@
         <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6962,7 +6974,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>81</v>
@@ -7004,7 +7016,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>92</v>
@@ -7045,10 +7057,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7071,13 +7083,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7089,7 +7101,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -7128,7 +7140,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7137,7 +7149,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -7169,10 +7181,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7195,13 +7207,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7252,7 +7264,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7293,10 +7305,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7322,13 +7334,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7354,13 +7366,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7378,7 +7390,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7405,13 +7417,13 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7419,10 +7431,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7445,13 +7457,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7502,7 +7514,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7517,25 +7529,25 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7543,10 +7555,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7569,13 +7581,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7626,7 +7638,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7641,10 +7653,10 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -7653,24 +7665,24 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7693,13 +7705,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7750,7 +7762,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7765,10 +7777,10 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7777,24 +7789,24 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7817,13 +7829,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7874,7 +7886,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7901,10 +7913,10 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7915,10 +7927,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7944,10 +7956,10 @@
         <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7974,31 +7986,31 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8025,24 +8037,24 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8068,10 +8080,10 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8098,31 +8110,31 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8149,24 +8161,24 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8189,13 +8201,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8246,7 +8258,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8261,22 +8273,22 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
@@ -8287,10 +8299,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8313,13 +8325,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8370,7 +8382,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8400,7 +8412,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8411,10 +8423,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8443,7 +8455,7 @@
         <v>139</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>141</v>
@@ -8484,19 +8496,19 @@
         <v>81</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8526,7 +8538,7 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8537,10 +8549,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8563,19 +8575,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8624,7 +8636,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8639,22 +8651,22 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8665,10 +8677,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8694,20 +8706,20 @@
         <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>81</v>
@@ -8731,10 +8743,10 @@
         <v>161</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8752,7 +8764,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8779,10 +8791,10 @@
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8793,10 +8805,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8819,17 +8831,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8878,7 +8890,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8893,22 +8905,22 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>81</v>
@@ -8919,10 +8931,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8948,14 +8960,14 @@
         <v>106</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -9004,7 +9016,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9013,7 +9025,7 @@
         <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -9031,10 +9043,10 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -9045,10 +9057,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9074,16 +9086,16 @@
         <v>112</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -9132,7 +9144,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9147,22 +9159,22 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -9173,10 +9185,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9199,13 +9211,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9256,7 +9268,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9280,13 +9292,13 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -9297,10 +9309,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9323,13 +9335,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9380,7 +9392,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9410,7 +9422,7 @@
         <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9421,10 +9433,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9453,7 +9465,7 @@
         <v>139</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>141</v>
@@ -9506,7 +9518,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9536,7 +9548,7 @@
         <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9547,14 +9559,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9576,10 +9588,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>141</v>
@@ -9634,7 +9646,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9675,10 +9687,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9704,10 +9716,10 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9719,46 +9731,46 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9773,7 +9785,7 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9782,13 +9794,13 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9799,10 +9811,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9825,16 +9837,16 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9884,7 +9896,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>92</v>
@@ -9899,25 +9911,25 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9925,10 +9937,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9951,13 +9963,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10008,7 +10020,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10032,13 +10044,13 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>
@@ -10049,10 +10061,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10075,13 +10087,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10132,7 +10144,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10162,7 +10174,7 @@
         <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>
@@ -10173,10 +10185,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10205,7 +10217,7 @@
         <v>139</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>141</v>
@@ -10246,19 +10258,19 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10288,7 +10300,7 @@
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>81</v>
@@ -10299,10 +10311,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10325,16 +10337,16 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10384,7 +10396,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10414,7 +10426,7 @@
         <v>135</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10425,10 +10437,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10451,13 +10463,13 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10508,7 +10520,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10538,7 +10550,7 @@
         <v>135</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10549,10 +10561,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10575,13 +10587,13 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10632,7 +10644,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>92</v>
@@ -10647,13 +10659,13 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10662,7 +10674,7 @@
         <v>135</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
@@ -10673,10 +10685,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10702,10 +10714,10 @@
         <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10732,31 +10744,31 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10780,13 +10792,13 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>81</v>
@@ -10797,10 +10809,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10823,13 +10835,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10880,7 +10892,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10904,7 +10916,7 @@
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10921,10 +10933,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10947,23 +10959,23 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>81</v>
@@ -11008,7 +11020,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11035,7 +11047,7 @@
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>135</v>
@@ -11049,10 +11061,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11078,10 +11090,10 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11108,31 +11120,31 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11173,10 +11185,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11199,13 +11211,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11256,7 +11268,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11268,7 +11280,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -11297,10 +11309,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11323,13 +11335,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11380,7 +11392,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11410,7 +11422,7 @@
         <v>81</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>81</v>
@@ -11421,10 +11433,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11453,7 +11465,7 @@
         <v>139</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>141</v>
@@ -11506,7 +11518,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11536,7 +11548,7 @@
         <v>81</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>81</v>
@@ -11547,14 +11559,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11576,10 +11588,10 @@
         <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>141</v>
@@ -11634,7 +11646,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11675,10 +11687,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11701,13 +11713,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11758,7 +11770,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11785,7 +11797,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>135</v>
@@ -11799,10 +11811,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11828,10 +11840,10 @@
         <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11882,7 +11894,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11923,10 +11935,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11949,13 +11961,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12006,7 +12018,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12033,7 +12045,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>135</v>
@@ -12047,10 +12059,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12073,13 +12085,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12130,7 +12142,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12157,7 +12169,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>135</v>
@@ -12171,10 +12183,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12200,10 +12212,10 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12230,31 +12242,31 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12281,7 +12293,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>135</v>
@@ -12295,10 +12307,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12324,10 +12336,10 @@
         <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12354,31 +12366,31 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12419,10 +12431,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12445,16 +12457,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12504,7 +12516,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12531,10 +12543,10 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>81</v>
@@ -12545,10 +12557,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12571,13 +12583,13 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12628,7 +12640,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12658,7 +12670,7 @@
         <v>81</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>81</v>
@@ -12669,10 +12681,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12701,7 +12713,7 @@
         <v>139</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>141</v>
@@ -12754,7 +12766,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12784,7 +12796,7 @@
         <v>81</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>81</v>
@@ -12795,14 +12807,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12824,10 +12836,10 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>141</v>
@@ -12882,7 +12894,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -12923,10 +12935,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12949,13 +12961,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13006,7 +13018,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13033,10 +13045,10 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>81</v>
@@ -13047,10 +13059,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13073,13 +13085,13 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13130,7 +13142,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13145,7 +13157,7 @@
         <v>104</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -13157,10 +13169,10 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>81</v>
@@ -13171,10 +13183,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13197,13 +13209,13 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13254,7 +13266,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13281,10 +13293,10 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>81</v>
@@ -13295,10 +13307,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13321,13 +13333,13 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13378,7 +13390,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13419,10 +13431,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13445,13 +13457,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13502,7 +13514,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13532,7 +13544,7 @@
         <v>81</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>81</v>
@@ -13543,10 +13555,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13575,7 +13587,7 @@
         <v>139</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>141</v>
@@ -13628,7 +13640,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13658,7 +13670,7 @@
         <v>81</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>81</v>
@@ -13669,14 +13681,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13698,10 +13710,10 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>141</v>
@@ -13756,7 +13768,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13797,10 +13809,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13823,13 +13835,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13880,7 +13892,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -13921,10 +13933,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13947,13 +13959,13 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14004,7 +14016,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14045,10 +14057,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14074,10 +14086,10 @@
         <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14104,31 +14116,31 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14169,10 +14181,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14195,16 +14207,16 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14242,17 +14254,17 @@
         <v>81</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>92</v>
@@ -14293,13 +14305,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>81</v>
@@ -14321,16 +14333,16 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14380,7 +14392,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>92</v>
@@ -14395,13 +14407,13 @@
         <v>104</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -14421,10 +14433,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14447,16 +14459,16 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14506,7 +14518,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -563,6 +563,9 @@
     <t>This is generally only used for the status of "not-done". The reason for performing the immunization event is captured in reasonCode, not here.</t>
   </si>
   <si>
+    <t>see mapping [VF_immunizationStatusReason](ConceptMap-VF-immunizationStatusReason.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/immunizationStatusReason</t>
   </si>
   <si>
@@ -588,6 +591,9 @@
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
+    <t>see mapping [VF_inferredCVX](ConceptMap-VF-inferredCVX.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/inferredCVX</t>
   </si>
   <si>
@@ -843,10 +849,16 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-332-1:If not null then source value from (undefined) {null}</t>
-  </si>
-  <si>
-    <t>332-1: source value if not null</t>
+ii-24-332-1:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03-.01) {null}</t>
+  </si>
+  <si>
+    <t>332-1: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.03-.01) if not null</t>
+  </si>
+  <si>
+    <t>Immun.Immunization.ImmunizationNameIEN</t>
+  </si>
+  <si>
+    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.Extension[VaccinationExtension].CDCName,Vaccination.Extension[VaccinationExtension].Source,Vaccination.AdministrationSite.Description,Vaccination.Manufacturer[VA.Manufacturer].Description</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -1011,7 +1023,7 @@
     <t>An indication that the content of the record is based on information from the person who administered the vaccine. This reflects the context under which the data was originally recorded.</t>
   </si>
   <si>
-    <t>Reflects the “reliability” of the content.</t>
+    <t>see mapping [VF_immunizationPrimarySource](ConceptMap-VF-immunizationPrimarySource.html)</t>
   </si>
   <si>
     <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (9000010.11-1301)</t>
@@ -1030,118 +1042,6 @@
   </si>
   <si>
     <t>FiveWs.source</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
-</t>
-  </si>
-  <si>
-    <t>Mapping from permitted to transmitted</t>
-  </si>
-  <si>
-    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
-  </si>
-  <si>
-    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension.extension</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(ConceptMap)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ConceptMap/VF-immunizationPrimarySource</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource.value</t>
-  </si>
-  <si>
-    <t>Primitive value for boolean</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>boolean.value</t>
   </si>
   <si>
     <t>Immunization.reportOrigin</t>
@@ -2357,12 +2257,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR97"/>
+  <dimension ref="A1:AR89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="80.68359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.7890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="61.234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.78125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="20.203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2384,7 +2284,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="89.65625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -3986,9 +3886,11 @@
       <c r="X13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Y13" s="2"/>
+      <c r="Y13" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -4018,10 +3920,10 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>165</v>
@@ -4030,13 +3932,13 @@
         <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>81</v>
@@ -4047,10 +3949,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4076,10 +3978,10 @@
         <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4108,9 +4010,11 @@
       <c r="X14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Y14" s="2"/>
+      <c r="Y14" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4128,7 +4032,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>92</v>
@@ -4137,42 +4041,42 @@
         <v>92</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4195,13 +4099,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4252,7 +4156,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4282,7 +4186,7 @@
         <v>81</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -4293,10 +4197,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4325,7 +4229,7 @@
         <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>141</v>
@@ -4366,19 +4270,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4408,7 +4312,7 @@
         <v>81</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>81</v>
@@ -4419,10 +4323,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4445,19 +4349,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4506,7 +4410,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4533,10 +4437,10 @@
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -4547,10 +4451,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4573,13 +4477,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4630,7 +4534,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4660,7 +4564,7 @@
         <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4671,10 +4575,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4703,7 +4607,7 @@
         <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>141</v>
@@ -4744,19 +4648,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4786,7 +4690,7 @@
         <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4797,10 +4701,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4826,16 +4730,16 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4845,7 +4749,7 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>81</v>
@@ -4884,7 +4788,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4899,7 +4803,7 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4911,10 +4815,10 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4925,10 +4829,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4951,16 +4855,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5010,7 +4914,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5037,10 +4941,10 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>81</v>
@@ -5051,10 +4955,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5080,14 +4984,14 @@
         <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -5136,7 +5040,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5151,10 +5055,10 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -5163,10 +5067,10 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>81</v>
@@ -5177,10 +5081,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5203,17 +5107,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5262,7 +5166,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5289,10 +5193,10 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>81</v>
@@ -5303,10 +5207,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5329,19 +5233,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5390,7 +5294,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5417,10 +5321,10 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>81</v>
@@ -5431,10 +5335,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5457,19 +5361,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5518,7 +5422,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5530,25 +5434,25 @@
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>81</v>
@@ -5559,14 +5463,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5585,13 +5489,13 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5642,7 +5546,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5657,25 +5561,25 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -5683,10 +5587,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5709,13 +5613,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5766,7 +5670,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5781,25 +5685,25 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -5807,10 +5711,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5833,16 +5737,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5880,17 +5784,17 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5914,30 +5818,30 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>81</v>
@@ -5959,16 +5863,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6018,7 +5922,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>92</v>
@@ -6033,36 +5937,36 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6085,13 +5989,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6142,7 +6046,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6157,10 +6061,10 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
@@ -6172,10 +6076,10 @@
         <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -6183,10 +6087,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6209,16 +6113,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6268,7 +6172,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6283,25 +6187,25 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -6309,10 +6213,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6335,15 +6239,17 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -6368,13 +6274,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -6392,7 +6298,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>198</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6404,7 +6310,7 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -6419,13 +6325,13 @@
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>81</v>
@@ -6433,10 +6339,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6447,10 +6353,10 @@
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
@@ -6459,13 +6365,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>138</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6504,50 +6410,52 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>205</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>345</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>81</v>
@@ -6555,14 +6463,12 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6574,7 +6480,7 @@
         <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
@@ -6583,17 +6489,15 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6642,25 +6546,25 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>205</v>
+        <v>349</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6669,24 +6573,24 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>135</v>
+        <v>355</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>135</v>
+        <v>356</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6700,7 +6604,7 @@
         <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
@@ -6709,13 +6613,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>196</v>
+        <v>359</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>197</v>
+        <v>360</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6766,7 +6670,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>358</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6775,16 +6679,16 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -6793,24 +6697,24 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>199</v>
+        <v>364</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6821,7 +6725,7 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6833,13 +6737,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>138</v>
+        <v>367</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6878,31 +6782,31 @@
         <v>81</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>366</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6917,10 +6821,10 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6931,10 +6835,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6942,7 +6846,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>92</v>
@@ -6957,24 +6861,22 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>81</v>
@@ -6992,13 +6894,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -7016,10 +6918,10 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>92</v>
@@ -7028,7 +6930,7 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -7043,24 +6945,24 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>135</v>
+        <v>378</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7068,7 +6970,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>92</v>
@@ -7083,13 +6985,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>352</v>
+        <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7101,7 +7003,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -7116,13 +7018,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -7140,7 +7042,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7149,7 +7051,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -7167,24 +7069,24 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>135</v>
+        <v>386</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7198,7 +7100,7 @@
         <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>81</v>
@@ -7207,13 +7109,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>251</v>
+        <v>389</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7264,7 +7166,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7276,25 +7178,25 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>395</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -7305,10 +7207,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7331,17 +7233,15 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>198</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -7366,13 +7266,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7390,7 +7290,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>200</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7402,7 +7302,7 @@
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -7417,13 +7317,13 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>369</v>
+        <v>201</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7431,24 +7331,24 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
@@ -7457,15 +7357,17 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>138</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>139</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7502,52 +7404,52 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>207</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>379</v>
+        <v>201</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7555,10 +7457,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7578,19 +7480,23 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7638,7 +7544,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7653,36 +7559,36 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7693,32 +7599,36 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I43" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I43" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="R43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7738,13 +7648,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7762,7 +7672,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7777,10 +7687,10 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7789,24 +7699,24 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7820,25 +7730,27 @@
         <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>399</v>
+        <v>197</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7886,7 +7798,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7901,22 +7813,22 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>81</v>
+        <v>427</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7927,10 +7839,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7950,19 +7862,21 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7986,13 +7900,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8010,7 +7924,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8019,7 +7933,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -8037,24 +7951,24 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8068,25 +7982,29 @@
         <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -8110,13 +8028,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -8134,7 +8052,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8149,36 +8067,36 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8189,25 +8107,25 @@
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8258,13 +8176,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -8273,22 +8191,22 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
@@ -8299,10 +8217,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8325,13 +8243,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8382,7 +8300,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8412,7 +8330,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8423,10 +8341,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8455,7 +8373,7 @@
         <v>139</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>141</v>
@@ -8496,19 +8414,19 @@
         <v>81</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8538,7 +8456,7 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8549,45 +8467,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I50" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>432</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>435</v>
+        <v>141</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>436</v>
+        <v>147</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8636,37 +8554,37 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>442</v>
+        <v>135</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8677,10 +8595,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8691,41 +8609,37 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>446</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8740,13 +8654,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>161</v>
+        <v>464</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8764,7 +8678,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8779,7 +8693,7 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
@@ -8788,13 +8702,13 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8805,10 +8719,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8816,7 +8730,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>92</v>
@@ -8831,18 +8745,18 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>195</v>
+        <v>471</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8890,10 +8804,10 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>92</v>
@@ -8905,25 +8819,25 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>426</v>
+        <v>477</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>81</v>
@@ -8931,10 +8845,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8945,7 +8859,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8957,18 +8871,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>106</v>
+        <v>482</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>465</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -9016,16 +8928,16 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>467</v>
+        <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -9040,13 +8952,13 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>485</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -9057,10 +8969,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9074,29 +8986,25 @@
         <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>470</v>
+        <v>198</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -9144,7 +9052,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>474</v>
+        <v>200</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9156,25 +9064,25 @@
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>477</v>
+        <v>201</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -9185,14 +9093,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9208,18 +9116,20 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>479</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>480</v>
+        <v>139</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -9256,19 +9166,19 @@
         <v>81</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>478</v>
+        <v>207</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9280,7 +9190,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -9292,13 +9202,13 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>484</v>
+        <v>201</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -9309,10 +9219,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9332,18 +9242,20 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>195</v>
+        <v>491</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>492</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -9392,7 +9304,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>198</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9404,7 +9316,7 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -9419,10 +9331,10 @@
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>199</v>
+        <v>496</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9433,21 +9345,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -9456,20 +9368,18 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>138</v>
+        <v>309</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>139</v>
+        <v>498</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9518,19 +9428,19 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>205</v>
+        <v>500</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -9545,10 +9455,10 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>199</v>
+        <v>501</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9559,46 +9469,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>138</v>
+        <v>503</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -9646,37 +9552,37 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>135</v>
+        <v>510</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9687,10 +9593,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9701,25 +9607,25 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9731,7 +9637,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9746,13 +9652,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>496</v>
+        <v>334</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9770,13 +9676,13 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
@@ -9785,7 +9691,7 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>499</v>
+        <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9794,13 +9700,13 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9811,10 +9717,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9822,32 +9728,30 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9896,13 +9800,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -9911,25 +9815,25 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>511</v>
+        <v>135</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9937,10 +9841,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9951,32 +9855,36 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>514</v>
+        <v>253</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="R61" t="s" s="2">
         <v>81</v>
       </c>
@@ -10020,13 +9928,13 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
@@ -10044,13 +9952,13 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>517</v>
+        <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>519</v>
+        <v>135</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>
@@ -10061,10 +9969,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10075,7 +9983,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -10087,13 +9995,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>196</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>197</v>
+        <v>530</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10120,13 +10028,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -10144,19 +10052,19 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>198</v>
+        <v>528</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -10174,7 +10082,7 @@
         <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>
@@ -10185,14 +10093,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10211,17 +10119,15 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>138</v>
+        <v>447</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>139</v>
+        <v>534</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -10258,19 +10164,19 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>205</v>
+        <v>533</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10282,7 +10188,7 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>143</v>
+        <v>536</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -10300,7 +10206,7 @@
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>81</v>
@@ -10311,10 +10217,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10334,20 +10240,18 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>523</v>
+        <v>197</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>524</v>
+        <v>198</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -10396,7 +10300,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>527</v>
+        <v>200</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10408,7 +10312,7 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -10423,10 +10327,10 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>528</v>
+        <v>201</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10437,21 +10341,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -10460,18 +10364,20 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>305</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>530</v>
+        <v>139</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10520,19 +10426,19 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>532</v>
+        <v>207</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -10547,10 +10453,10 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>533</v>
+        <v>201</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10561,42 +10467,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>535</v>
+        <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>536</v>
+        <v>457</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10644,37 +10554,37 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>538</v>
+        <v>459</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>539</v>
+        <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>540</v>
+        <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>541</v>
+        <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
@@ -10685,10 +10595,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10699,7 +10609,7 @@
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -10711,13 +10621,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10744,13 +10654,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>546</v>
+        <v>81</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>547</v>
+        <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10768,13 +10678,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -10792,13 +10702,13 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>81</v>
+        <v>543</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>549</v>
+        <v>135</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>81</v>
@@ -10809,10 +10719,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10823,7 +10733,7 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10835,13 +10745,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>551</v>
+        <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10892,13 +10802,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
@@ -10916,7 +10826,7 @@
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>553</v>
+        <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10933,10 +10843,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10953,30 +10863,26 @@
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q69" t="s" s="2">
-        <v>558</v>
-      </c>
+      <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
         <v>81</v>
       </c>
@@ -11020,7 +10926,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11047,7 +10953,7 @@
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>135</v>
@@ -11061,10 +10967,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11075,7 +10981,7 @@
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -11087,13 +10993,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>171</v>
+        <v>309</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11120,13 +11026,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -11144,13 +11050,13 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
@@ -11171,7 +11077,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>135</v>
@@ -11185,10 +11091,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11211,13 +11117,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>479</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11244,13 +11150,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>81</v>
+        <v>558</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11268,7 +11174,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11280,7 +11186,7 @@
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>568</v>
+        <v>104</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -11295,7 +11201,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>81</v>
+        <v>560</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>135</v>
@@ -11309,10 +11215,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11335,13 +11241,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>196</v>
+        <v>562</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>197</v>
+        <v>563</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11368,13 +11274,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>81</v>
+        <v>565</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11392,7 +11298,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>198</v>
+        <v>561</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11404,7 +11310,7 @@
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -11422,7 +11328,7 @@
         <v>81</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>81</v>
@@ -11433,14 +11339,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11459,16 +11365,16 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>138</v>
+        <v>447</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>139</v>
+        <v>567</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>201</v>
+        <v>568</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>141</v>
+        <v>569</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11518,7 +11424,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>205</v>
+        <v>566</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11530,7 +11436,7 @@
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>81</v>
@@ -11545,10 +11451,10 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>199</v>
+        <v>571</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>81</v>
@@ -11559,46 +11465,42 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>489</v>
+        <v>198</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11646,19 +11548,19 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>491</v>
+        <v>200</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
@@ -11676,7 +11578,7 @@
         <v>81</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>81</v>
@@ -11687,21 +11589,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>81</v>
@@ -11713,15 +11615,17 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>573</v>
+        <v>139</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11770,19 +11674,19 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>572</v>
+        <v>207</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
@@ -11797,10 +11701,10 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>81</v>
@@ -11811,42 +11715,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>577</v>
+        <v>457</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11894,19 +11802,19 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>576</v>
+        <v>459</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -11935,10 +11843,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11961,13 +11869,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12018,7 +11926,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12045,10 +11953,10 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>81</v>
@@ -12059,10 +11967,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12076,7 +11984,7 @@
         <v>92</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>81</v>
@@ -12085,13 +11993,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>305</v>
+        <v>580</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12142,7 +12050,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12157,7 +12065,7 @@
         <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
@@ -12169,10 +12077,10 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>135</v>
+        <v>585</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>81</v>
@@ -12183,10 +12091,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12197,7 +12105,7 @@
         <v>82</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -12209,13 +12117,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>171</v>
+        <v>253</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12242,13 +12150,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>590</v>
+        <v>81</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>591</v>
+        <v>81</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -12266,13 +12174,13 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
@@ -12293,10 +12201,10 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>135</v>
+        <v>590</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>81</v>
@@ -12307,10 +12215,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12321,7 +12229,7 @@
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>81</v>
@@ -12333,13 +12241,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>171</v>
+        <v>447</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12366,13 +12274,13 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>596</v>
+        <v>81</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>597</v>
+        <v>81</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -12390,13 +12298,13 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>81</v>
@@ -12431,10 +12339,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12445,7 +12353,7 @@
         <v>82</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -12457,17 +12365,15 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>479</v>
+        <v>197</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>599</v>
+        <v>198</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -12516,19 +12422,19 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>598</v>
+        <v>200</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>81</v>
@@ -12543,10 +12449,10 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>602</v>
+        <v>81</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>603</v>
+        <v>201</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>81</v>
@@ -12557,21 +12463,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
@@ -12583,15 +12489,17 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12640,19 +12548,19 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
@@ -12670,7 +12578,7 @@
         <v>81</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>81</v>
@@ -12681,14 +12589,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>137</v>
+        <v>456</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12701,24 +12609,26 @@
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>139</v>
+        <v>457</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>201</v>
+        <v>458</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12766,7 +12676,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>205</v>
+        <v>459</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12796,7 +12706,7 @@
         <v>81</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>81</v>
@@ -12807,46 +12717,42 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>489</v>
+        <v>598</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -12894,19 +12800,19 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>491</v>
+        <v>597</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -12935,10 +12841,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12961,13 +12867,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>305</v>
+        <v>350</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13018,7 +12924,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13045,10 +12951,10 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>300</v>
+        <v>135</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>81</v>
@@ -13059,10 +12965,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13073,10 +12979,10 @@
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>81</v>
@@ -13085,13 +12991,13 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>612</v>
+        <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13118,13 +13024,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>81</v>
+        <v>606</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>81</v>
+        <v>607</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -13142,13 +13048,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -13157,7 +13063,7 @@
         <v>104</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>615</v>
+        <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -13169,10 +13075,10 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>616</v>
+        <v>81</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>617</v>
+        <v>135</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>81</v>
@@ -13183,10 +13089,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13194,7 +13100,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>92</v>
@@ -13209,15 +13115,17 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>251</v>
+        <v>609</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13254,22 +13162,20 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>92</v>
@@ -13293,10 +13199,10 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>621</v>
+        <v>81</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>622</v>
+        <v>135</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>81</v>
@@ -13307,12 +13213,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>81</v>
       </c>
@@ -13321,10 +13229,10 @@
         <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>81</v>
@@ -13333,15 +13241,17 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>479</v>
+        <v>197</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -13390,13 +13300,13 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
@@ -13405,13 +13315,13 @@
         <v>104</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>81</v>
+        <v>615</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>81</v>
+        <v>616</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>81</v>
+        <v>617</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -13431,10 +13341,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13457,15 +13367,17 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>195</v>
+        <v>609</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>196</v>
+        <v>619</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13514,7 +13426,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>198</v>
+        <v>618</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13526,7 +13438,7 @@
         <v>81</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>81</v>
@@ -13544,1021 +13456,17 @@
         <v>81</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AQ90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR90" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AC95" s="2"/>
-      <c r="AD95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR97" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR97">
+  <autoFilter ref="A1:AR89">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14568,7 +13476,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="619">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -849,16 +849,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-332-1:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03-.01) {null}</t>
-  </si>
-  <si>
-    <t>332-1: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.03-.01) if not null</t>
-  </si>
-  <si>
-    <t>Immun.Immunization.ImmunizationNameIEN</t>
-  </si>
-  <si>
-    <t>Vaccination.MaxDoseQuantity,Vaccination.OrderItem,Vaccination.Extension[VaccinationExtension].CDCName,Vaccination.Extension[VaccinationExtension].Source,Vaccination.AdministrationSite.Description,Vaccination.Manufacturer[VA.Manufacturer].Description</t>
+ii-24-332-1:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.01) {null}</t>
+  </si>
+  <si>
+    <t>332-1: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if not null</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -5440,19 +5434,19 @@
         <v>268</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>81</v>
@@ -5463,14 +5457,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5489,13 +5483,13 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5546,7 +5540,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5561,25 +5555,25 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -5587,10 +5581,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5613,13 +5607,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5670,7 +5664,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5685,25 +5679,25 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -5711,10 +5705,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5737,16 +5731,16 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5784,7 +5778,7 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5794,7 +5788,7 @@
         <v>206</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5818,30 +5812,30 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AR28" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>81</v>
@@ -5863,16 +5857,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5922,7 +5916,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>92</v>
@@ -5937,36 +5931,36 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="AN29" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AP29" t="s" s="2">
+      <c r="AR29" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5989,13 +5983,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6046,7 +6040,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6061,25 +6055,25 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -6087,10 +6081,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6116,13 +6110,13 @@
         <v>253</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6172,7 +6166,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6187,25 +6181,25 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -6213,10 +6207,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6242,13 +6236,13 @@
         <v>171</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6274,14 +6268,14 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Y32" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
       </c>
@@ -6298,7 +6292,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6325,13 +6319,13 @@
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>81</v>
@@ -6339,10 +6333,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6365,13 +6359,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6422,7 +6416,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6437,25 +6431,25 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>81</v>
@@ -6463,10 +6457,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6489,13 +6483,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6546,7 +6540,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6561,36 +6555,36 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>357</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6616,10 +6610,10 @@
         <v>197</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6670,7 +6664,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6685,36 +6679,36 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6737,13 +6731,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6794,7 +6788,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6821,10 +6815,10 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6835,10 +6829,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6864,10 +6858,10 @@
         <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6894,13 +6888,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6918,7 +6912,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6945,24 +6939,24 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6988,10 +6982,10 @@
         <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7018,13 +7012,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -7042,7 +7036,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7069,24 +7063,24 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7109,13 +7103,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7166,7 +7160,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7181,22 +7175,22 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -7207,10 +7201,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7331,10 +7325,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7457,10 +7451,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7483,19 +7477,19 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7544,7 +7538,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7559,22 +7553,22 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
@@ -7585,10 +7579,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7614,20 +7608,20 @@
         <v>112</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>81</v>
@@ -7651,28 +7645,28 @@
         <v>161</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7699,10 +7693,10 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7713,10 +7707,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7742,14 +7736,14 @@
         <v>197</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7798,7 +7792,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7813,22 +7807,22 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7839,10 +7833,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7868,14 +7862,14 @@
         <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7924,7 +7918,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7933,7 +7927,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7951,10 +7945,10 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
@@ -7965,10 +7959,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7994,16 +7988,16 @@
         <v>112</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8052,7 +8046,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8067,22 +8061,22 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
@@ -8093,10 +8087,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8119,13 +8113,13 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8176,7 +8170,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8200,13 +8194,13 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
@@ -8217,10 +8211,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8341,10 +8335,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8467,14 +8461,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8496,10 +8490,10 @@
         <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>141</v>
@@ -8554,7 +8548,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8595,10 +8589,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8624,10 +8618,10 @@
         <v>171</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8639,29 +8633,29 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="T51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Y51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8678,7 +8672,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8693,22 +8687,22 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8719,10 +8713,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8745,16 +8739,16 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8804,7 +8798,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>92</v>
@@ -8819,25 +8813,25 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AQ52" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>81</v>
@@ -8845,10 +8839,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8871,13 +8865,13 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8928,7 +8922,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8952,13 +8946,13 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8969,10 +8963,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9093,10 +9087,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9219,10 +9213,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9245,16 +9239,16 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9304,7 +9298,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9334,7 +9328,7 @@
         <v>135</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9345,10 +9339,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9371,13 +9365,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9428,7 +9422,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9458,7 +9452,7 @@
         <v>135</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9469,10 +9463,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9495,13 +9489,13 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9552,7 +9546,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>92</v>
@@ -9567,13 +9561,13 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9582,7 +9576,7 @@
         <v>135</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9593,10 +9587,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9622,10 +9616,10 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9652,13 +9646,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9676,7 +9670,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9700,13 +9694,13 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9717,10 +9711,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9743,13 +9737,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9800,7 +9794,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9824,7 +9818,7 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9841,10 +9835,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9870,20 +9864,20 @@
         <v>253</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q61" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R61" t="s" s="2">
         <v>81</v>
@@ -9928,7 +9922,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9955,7 +9949,7 @@
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>135</v>
@@ -9969,10 +9963,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9998,10 +9992,10 @@
         <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10028,13 +10022,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -10052,7 +10046,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10093,10 +10087,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10119,13 +10113,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10176,7 +10170,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10188,7 +10182,7 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -10217,10 +10211,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10341,10 +10335,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10467,14 +10461,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10496,10 +10490,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>141</v>
@@ -10554,7 +10548,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10595,10 +10589,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10624,10 +10618,10 @@
         <v>197</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10678,7 +10672,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10705,7 +10699,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>135</v>
@@ -10719,10 +10713,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10748,10 +10742,10 @@
         <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10802,7 +10796,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10843,10 +10837,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10869,13 +10863,13 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10926,7 +10920,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10953,7 +10947,7 @@
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>135</v>
@@ -10967,10 +10961,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10993,13 +10987,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11050,7 +11044,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11077,7 +11071,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>135</v>
@@ -11091,10 +11085,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11120,10 +11114,10 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11150,13 +11144,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11174,7 +11168,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11201,7 +11195,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>135</v>
@@ -11215,10 +11209,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11244,10 +11238,10 @@
         <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11274,13 +11268,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11298,7 +11292,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11339,10 +11333,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11365,16 +11359,16 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11424,7 +11418,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11451,10 +11445,10 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>81</v>
@@ -11465,10 +11459,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11589,10 +11583,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11715,14 +11709,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11744,10 +11738,10 @@
         <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>141</v>
@@ -11802,7 +11796,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11843,10 +11837,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11869,13 +11863,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11926,7 +11920,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11953,10 +11947,10 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>81</v>
@@ -11967,10 +11961,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11993,13 +11987,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12050,7 +12044,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12065,22 +12059,22 @@
         <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>81</v>
@@ -12091,10 +12085,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12120,10 +12114,10 @@
         <v>253</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12174,7 +12168,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12201,10 +12195,10 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>81</v>
@@ -12215,10 +12209,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12241,13 +12235,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12298,7 +12292,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12339,10 +12333,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12463,10 +12457,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12589,14 +12583,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12618,10 +12612,10 @@
         <v>138</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>141</v>
@@ -12676,7 +12670,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12717,10 +12711,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12746,10 +12740,10 @@
         <v>197</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12800,7 +12794,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -12841,10 +12835,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12867,13 +12861,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12924,7 +12918,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -12965,10 +12959,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12994,10 +12988,10 @@
         <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13024,13 +13018,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -13048,7 +13042,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13089,10 +13083,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13115,16 +13109,16 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13162,7 +13156,7 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
@@ -13172,7 +13166,7 @@
         <v>206</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>92</v>
@@ -13213,13 +13207,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>81</v>
@@ -13244,13 +13238,13 @@
         <v>197</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13300,7 +13294,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>92</v>
@@ -13315,13 +13309,13 @@
         <v>104</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -13341,10 +13335,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13367,16 +13361,16 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13426,7 +13420,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -524,7 +524,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-297:If (9000010.11-.01 &gt; 9999999.14-.03) is CVX populated then fixed value #completed {null}ii-24-298:If (9000010.11-.01 &gt; 9999999.14-.01) is missing or unknown then exclude record {null}ii-24-299:If (9000010.11-.01 &gt; 9999999.14-.01) is text like 'contraindicated', 'refused', 'decline', 'not avail' then fixed value #not-done {null}</t>
+ii-24-297:If (9000010.11-.01 &gt; 9999999.14-.03) is CVX populated then fixed value #completed {true}ii-24-298:If (9000010.11-.01 &gt; 9999999.14-.01) is missing or unknown then exclude record {true}ii-24-299:If (9000010.11-.01 &gt; 9999999.14-.01) is text like 'contraindicated', 'refused', 'decline', 'not avail' then fixed value #not-done {true}</t>
   </si>
   <si>
     <t>299: fixed value = #not-done when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
@@ -570,7 +570,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-527:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_immunizationStatusReason {null}</t>
+ii-24-527:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_immunizationStatusReason {true}</t>
   </si>
   <si>
     <t>527: terminologyMaps using VF_immunizationStatusReason on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if V IMMUNIZATION - IMMUNIZATION null</t>
@@ -602,7 +602,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-528:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_inferredCVX {null}ii-24-332:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03) {null}</t>
+ii-24-528:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_inferredCVX {true}ii-24-332:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03) {true}</t>
   </si>
   <si>
     <t>332: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) if not null</t>
@@ -849,7 +849,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-332-1:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.01) {null}</t>
+ii-24-332-1:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.01) {true}</t>
   </si>
   <si>
     <t>332-1: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if not null</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3934" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,7 +602,193 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ii-24-528:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_inferredCVX {true}ii-24-332:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03) {true}</t>
+ii-24-528:If V IMMUNIZATION - IMMUNIZATION null then terminologyMaps (9000010.11-.01 &gt; 9999999.14-.01) using VF_inferredCVX {true}</t>
+  </si>
+  <si>
+    <t>528: terminologyMaps using VF_inferredCVX on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (9000010.11-.01 &gt; 9999999.14-.01) if V IMMUNIZATION - IMMUNIZATION null</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>RXA-5</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx</t>
+  </si>
+  <si>
+    <t>va-cvx</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.system</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ii-24-332-2:If not null then fixed value http://hl7.org/fhir/sid/cvx {true}</t>
+  </si>
+  <si>
+    <t>332-2: fixed value = http://hl7.org/fhir/sid/cvx if not null</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.version</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.code</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ii-24-332:If not null then source value from (9000010.11-.01 &gt; 9999999.14-.03) {true}</t>
   </si>
   <si>
     <t>332: source value based on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (9000010.11-.01 &gt; 9999999.14-.03) if not null</t>
@@ -616,171 +802,15 @@
 Vaccination.OrderItem[Order].Code,Vaccination.Route.Code,Vaccination.OrderItem[Order].Code</t>
   </si>
   <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>RXA-5</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.id</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.extension</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/sid/ndc</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>1609-1: fixed value = http://hl7.org/fhir/sid/ndc</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>1609: source value based on V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
-  </si>
-  <si>
-    <t>Dim.ImmunizationLot.NDCCodeVAText</t>
-  </si>
-  <si>
     <t>C*E.1</t>
   </si>
   <si>
     <t>./code</t>
   </si>
   <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.display</t>
+  </si>
+  <si>
     <t>Immunization.vaccineCode.coding.display</t>
   </si>
   <si>
@@ -800,6 +830,9 @@
   </si>
   <si>
     <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-cvx.userSelected</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.userSelected</t>
@@ -830,6 +863,45 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Immunization.vaccineCode.coding:va-ndc</t>
+  </si>
+  <si>
+    <t>va-ndc</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/sid/ndc</t>
+  </si>
+  <si>
+    <t>1609-1: fixed value = http://hl7.org/fhir/sid/ndc</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.version</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.code</t>
+  </si>
+  <si>
+    <t>1609: source value based on V IMMUNIZATION - LOT &gt; IMMUNIZATION LOT - NDC CODE (VA) (9000010.11-.05 &gt; 9999999.41-.18)</t>
+  </si>
+  <si>
+    <t>Dim.ImmunizationLot.NDCCodeVAText</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.display</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:va-ndc.userSelected</t>
+  </si>
+  <si>
     <t>Immunization.vaccineCode.text</t>
   </si>
   <si>
@@ -868,7 +940,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -878,7 +950,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>333: source value based on V IMMUNIZATION - PATIENT NAME (9000010.11-.02)</t>
+    <t>333: reference based on V IMMUNIZATION - PATIENT NAME (9000010.11-.02)</t>
   </si>
   <si>
     <t>Immun.Immunization.PatientIEN</t>
@@ -2251,7 +2323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR89"/>
+  <dimension ref="A1:AR98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.234375" customWidth="true" bestFit="true"/>
@@ -4044,33 +4116,33 @@
         <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AR14" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AR14" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4093,13 +4165,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4150,7 +4222,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4180,7 +4252,7 @@
         <v>81</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -4191,10 +4263,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4223,7 +4295,7 @@
         <v>139</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>141</v>
@@ -4264,19 +4336,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4306,7 +4378,7 @@
         <v>81</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>81</v>
@@ -4317,10 +4389,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4343,19 +4415,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4392,19 +4464,17 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4431,10 +4501,10 @@
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -4445,12 +4515,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4468,19 +4540,23 @@
         <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4528,19 +4604,19 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4555,10 +4631,10 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4572,18 +4648,18 @@
         <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -4595,17 +4671,15 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4642,31 +4716,31 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4684,7 +4758,7 @@
         <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4695,46 +4769,44 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4743,7 +4815,7 @@
         <v>81</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>81</v>
@@ -4770,34 +4842,34 @@
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4809,10 +4881,10 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4823,10 +4895,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4840,7 +4912,7 @@
         <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>81</v>
@@ -4849,18 +4921,20 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4908,7 +4982,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4920,10 +4994,10 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -4935,10 +5009,10 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>81</v>
@@ -4949,10 +5023,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4966,7 +5040,7 @@
         <v>92</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>81</v>
@@ -4975,18 +5049,18 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
       </c>
@@ -5034,7 +5108,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5049,10 +5123,10 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -5061,10 +5135,10 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>81</v>
@@ -5075,10 +5149,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5092,7 +5166,7 @@
         <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>81</v>
@@ -5101,17 +5175,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5160,37 +5234,37 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM23" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>81</v>
@@ -5201,10 +5275,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5227,17 +5301,15 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>257</v>
       </c>
@@ -5332,7 +5404,7 @@
         <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5346,7 +5418,7 @@
         <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>81</v>
@@ -5355,19 +5427,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5416,7 +5488,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5428,16 +5500,16 @@
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>267</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5460,21 +5532,23 @@
         <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
@@ -5483,16 +5557,20 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5540,13 +5618,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -5555,25 +5633,25 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>281</v>
+        <v>215</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>81</v>
@@ -5581,10 +5659,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5598,7 +5676,7 @@
         <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
@@ -5607,13 +5685,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>195</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>196</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5664,7 +5742,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>198</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5676,28 +5754,28 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>290</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>292</v>
+        <v>199</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>81</v>
@@ -5705,42 +5783,42 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>295</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>139</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
+        <v>201</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>298</v>
+        <v>141</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5778,29 +5856,31 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>205</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5812,31 +5892,29 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>302</v>
+        <v>199</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5857,18 +5935,20 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>307</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5877,7 +5957,7 @@
         <v>81</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>81</v>
@@ -5916,10 +5996,10 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>92</v>
@@ -5931,36 +6011,36 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>231</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5974,24 +6054,26 @@
         <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -6040,7 +6122,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6055,10 +6137,10 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
@@ -6067,13 +6149,13 @@
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>81</v>
@@ -6081,10 +6163,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6092,7 +6174,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>92</v>
@@ -6107,18 +6189,18 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -6166,7 +6248,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6181,25 +6263,25 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>81</v>
@@ -6207,10 +6289,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>254</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6230,21 +6312,21 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>329</v>
+        <v>255</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -6268,13 +6350,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -6292,7 +6374,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>328</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6319,13 +6401,13 @@
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>325</v>
+        <v>259</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>335</v>
+        <v>260</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>81</v>
@@ -6333,10 +6415,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6350,25 +6432,29 @@
         <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>263</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>264</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6416,7 +6502,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>268</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6431,25 +6517,25 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>344</v>
+        <v>269</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>345</v>
+        <v>270</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>81</v>
@@ -6457,10 +6543,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6480,19 +6566,23 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>348</v>
+        <v>195</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6540,7 +6630,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6552,47 +6642,47 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>290</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>351</v>
+        <v>291</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>352</v>
+        <v>165</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6604,16 +6694,16 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>197</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6664,10 +6754,10 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>92</v>
@@ -6679,36 +6769,36 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>303</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>362</v>
+        <v>304</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6722,7 +6812,7 @@
         <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
@@ -6731,13 +6821,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>365</v>
+        <v>307</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>366</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>367</v>
+        <v>309</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6788,7 +6878,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>364</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6803,25 +6893,25 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>368</v>
+        <v>314</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>81</v>
@@ -6829,10 +6919,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6840,30 +6930,32 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>318</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6888,34 +6980,32 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>92</v>
@@ -6936,29 +7026,31 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>377</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>378</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6970,24 +7062,26 @@
         <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>171</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>379</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -7012,13 +7106,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -7036,10 +7130,10 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>378</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>92</v>
@@ -7051,36 +7145,36 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>331</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7103,13 +7197,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>387</v>
+        <v>330</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>388</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7160,7 +7254,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7175,25 +7269,25 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>394</v>
+        <v>339</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -7201,10 +7295,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7212,30 +7306,32 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>198</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -7284,7 +7380,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>200</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7296,28 +7392,28 @@
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>345</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>201</v>
+        <v>349</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7325,21 +7421,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -7351,16 +7447,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>139</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>203</v>
+        <v>353</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>141</v>
+        <v>354</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7386,43 +7482,43 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>207</v>
+        <v>351</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -7437,13 +7533,13 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7451,10 +7547,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7474,23 +7570,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>398</v>
+        <v>360</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>399</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7538,7 +7630,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7553,25 +7645,25 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>408</v>
+        <v>368</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>81</v>
+        <v>369</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>81</v>
@@ -7579,10 +7671,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7593,36 +7685,32 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>112</v>
+        <v>371</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>412</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7642,13 +7730,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7666,7 +7754,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7681,10 +7769,10 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7693,24 +7781,24 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7730,21 +7818,19 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>422</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7792,7 +7878,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7807,36 +7893,36 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7856,21 +7942,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>106</v>
+        <v>388</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>431</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7918,7 +8002,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7927,7 +8011,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>433</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7945,10 +8029,10 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>434</v>
+        <v>392</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
@@ -7959,10 +8043,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7976,29 +8060,25 @@
         <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>394</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -8022,13 +8102,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -8046,7 +8126,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8061,36 +8141,36 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8101,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -8110,16 +8190,16 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8146,13 +8226,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -8170,13 +8250,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -8194,27 +8274,27 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>449</v>
+        <v>406</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>450</v>
+        <v>407</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8228,7 +8308,7 @@
         <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -8237,13 +8317,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>197</v>
+        <v>410</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>198</v>
+        <v>411</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8294,7 +8374,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>200</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8306,25 +8386,25 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>201</v>
+        <v>417</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8335,21 +8415,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -8361,17 +8441,15 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8420,19 +8498,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -8450,7 +8528,7 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8461,14 +8539,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>453</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>453</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>454</v>
+        <v>137</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8481,26 +8559,24 @@
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>455</v>
+        <v>139</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>456</v>
+        <v>201</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O50" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8536,19 +8612,19 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>457</v>
+        <v>205</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8578,7 +8654,7 @@
         <v>81</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8589,10 +8665,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8615,16 +8691,20 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>171</v>
+        <v>421</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8633,7 +8713,7 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8648,13 +8728,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8672,7 +8752,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8687,22 +8767,22 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>465</v>
+        <v>427</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>81</v>
+        <v>428</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8713,10 +8793,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8724,37 +8804,39 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I52" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8774,13 +8856,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8798,10 +8880,10 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>92</v>
@@ -8813,25 +8895,25 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>478</v>
+        <v>81</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>81</v>
@@ -8839,10 +8921,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8853,10 +8935,10 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
@@ -8865,16 +8947,18 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>480</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8922,13 +9006,13 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
@@ -8937,22 +9021,22 @@
         <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8963,10 +9047,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8986,19 +9070,21 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>198</v>
+        <v>452</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>199</v>
+        <v>453</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -9046,7 +9132,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>200</v>
+        <v>455</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9055,10 +9141,10 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -9073,10 +9159,10 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>201</v>
+        <v>457</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -9087,44 +9173,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>139</v>
+        <v>459</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>203</v>
+        <v>460</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -9160,49 +9248,49 @@
         <v>81</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>207</v>
+        <v>463</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>81</v>
+        <v>465</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>201</v>
+        <v>466</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -9213,10 +9301,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9227,7 +9315,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -9239,17 +9327,15 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -9298,13 +9384,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -9322,13 +9408,13 @@
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>135</v>
+        <v>472</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9339,10 +9425,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9362,16 +9448,16 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>496</v>
+        <v>196</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>497</v>
+        <v>197</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9422,7 +9508,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>198</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9434,7 +9520,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -9449,10 +9535,10 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>499</v>
+        <v>199</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9463,41 +9549,43 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>501</v>
+        <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>139</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9546,37 +9634,37 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>504</v>
+        <v>205</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>508</v>
+        <v>199</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9587,14 +9675,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9607,22 +9695,26 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9646,13 +9738,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9670,7 +9762,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9682,7 +9774,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9694,13 +9786,13 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>514</v>
+        <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>515</v>
+        <v>135</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9711,10 +9803,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9725,25 +9817,25 @@
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>517</v>
+        <v>171</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>483</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9755,7 +9847,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -9770,13 +9862,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>81</v>
+        <v>485</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9794,13 +9886,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -9809,7 +9901,7 @@
         <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
@@ -9818,13 +9910,13 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>519</v>
+        <v>489</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>135</v>
+        <v>490</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>81</v>
@@ -9835,10 +9927,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9846,39 +9938,37 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>492</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>524</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>81</v>
       </c>
@@ -9922,10 +10012,10 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>92</v>
@@ -9937,25 +10027,25 @@
         <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>81</v>
+        <v>496</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>525</v>
+        <v>81</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>135</v>
+        <v>500</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>81</v>
@@ -9963,10 +10053,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9986,16 +10076,16 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>171</v>
+        <v>503</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10022,13 +10112,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>529</v>
+        <v>81</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -10046,7 +10136,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10070,13 +10160,13 @@
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>135</v>
+        <v>508</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>
@@ -10087,10 +10177,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10101,7 +10191,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -10113,13 +10203,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>445</v>
+        <v>195</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>532</v>
+        <v>196</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>533</v>
+        <v>197</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10170,19 +10260,19 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>531</v>
+        <v>198</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
@@ -10200,7 +10290,7 @@
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>81</v>
@@ -10211,21 +10301,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -10237,15 +10327,17 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -10282,31 +10374,31 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -10324,7 +10416,7 @@
         <v>81</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10335,21 +10427,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -10358,19 +10450,19 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>138</v>
+        <v>512</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>139</v>
+        <v>513</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>203</v>
+        <v>514</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>141</v>
+        <v>515</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10420,19 +10512,19 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>207</v>
+        <v>516</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -10447,10 +10539,10 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>201</v>
+        <v>517</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10461,46 +10553,42 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>138</v>
+        <v>330</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>455</v>
+        <v>519</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10548,19 +10636,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>457</v>
+        <v>521</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -10575,10 +10663,10 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>135</v>
+        <v>522</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
@@ -10589,10 +10677,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10600,28 +10688,28 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>197</v>
+        <v>524</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10672,10 +10760,10 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>92</v>
@@ -10687,22 +10775,22 @@
         <v>104</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>81</v>
+        <v>528</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>81</v>
+        <v>529</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>541</v>
+        <v>135</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>135</v>
+        <v>531</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>81</v>
@@ -10713,10 +10801,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10727,7 +10815,7 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10739,13 +10827,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10772,13 +10860,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>535</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10796,13 +10884,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
@@ -10820,13 +10908,13 @@
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>537</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>135</v>
+        <v>538</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>81</v>
@@ -10837,10 +10925,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10851,7 +10939,7 @@
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10863,13 +10951,13 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>307</v>
+        <v>540</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10920,13 +11008,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10944,10 +11032,10 @@
         <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>135</v>
@@ -10961,10 +11049,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10981,26 +11069,30 @@
         <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q70" s="2"/>
+      <c r="Q70" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="R70" t="s" s="2">
         <v>81</v>
       </c>
@@ -11044,7 +11136,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11071,7 +11163,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>135</v>
@@ -11085,10 +11177,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11114,10 +11206,10 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11144,13 +11236,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11168,7 +11260,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11195,7 +11287,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>558</v>
+        <v>81</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>135</v>
@@ -11209,10 +11301,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11223,7 +11315,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -11235,13 +11327,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>171</v>
+        <v>468</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11268,13 +11360,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11292,19 +11384,19 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>104</v>
+        <v>557</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>81</v>
@@ -11333,10 +11425,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11347,7 +11439,7 @@
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
@@ -11359,17 +11451,15 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>445</v>
+        <v>195</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>565</v>
+        <v>196</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -11418,19 +11508,19 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>81</v>
@@ -11445,10 +11535,10 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>569</v>
+        <v>199</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>81</v>
@@ -11459,21 +11549,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -11485,15 +11575,17 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11542,19 +11634,19 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
@@ -11572,7 +11664,7 @@
         <v>81</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>81</v>
@@ -11583,14 +11675,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>137</v>
+        <v>477</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11603,24 +11695,26 @@
         <v>81</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>139</v>
+        <v>478</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>203</v>
+        <v>479</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -11668,7 +11762,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>207</v>
+        <v>480</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11698,7 +11792,7 @@
         <v>81</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>81</v>
@@ -11709,46 +11803,42 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>455</v>
+        <v>562</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11796,19 +11886,19 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>457</v>
+        <v>561</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -11823,7 +11913,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>135</v>
@@ -11837,10 +11927,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11863,13 +11953,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>307</v>
+        <v>106</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11920,7 +12010,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11947,10 +12037,10 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>576</v>
+        <v>81</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>302</v>
+        <v>135</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>81</v>
@@ -11961,10 +12051,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11978,7 +12068,7 @@
         <v>92</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>81</v>
@@ -11987,13 +12077,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>578</v>
+        <v>330</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12044,7 +12134,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12059,7 +12149,7 @@
         <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>581</v>
+        <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
@@ -12071,10 +12161,10 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>583</v>
+        <v>135</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>81</v>
@@ -12085,10 +12175,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12111,13 +12201,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12168,7 +12258,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12195,10 +12285,10 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>588</v>
+        <v>135</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>81</v>
@@ -12209,10 +12299,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12235,13 +12325,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>445</v>
+        <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12268,13 +12358,13 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>81</v>
+        <v>579</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>81</v>
+        <v>580</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -12292,7 +12382,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12319,7 +12409,7 @@
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>81</v>
+        <v>581</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>135</v>
@@ -12333,10 +12423,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12359,13 +12449,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>198</v>
+        <v>583</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>199</v>
+        <v>584</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12392,13 +12482,13 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>81</v>
+        <v>585</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>81</v>
+        <v>586</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -12416,7 +12506,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>200</v>
+        <v>582</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12428,7 +12518,7 @@
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>81</v>
@@ -12446,7 +12536,7 @@
         <v>81</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>81</v>
@@ -12457,14 +12547,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12483,16 +12573,16 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>138</v>
+        <v>468</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>139</v>
+        <v>588</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>203</v>
+        <v>589</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>141</v>
+        <v>590</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12542,7 +12632,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>207</v>
+        <v>587</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12554,7 +12644,7 @@
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
@@ -12569,10 +12659,10 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>81</v>
+        <v>591</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>201</v>
+        <v>592</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>81</v>
@@ -12583,46 +12673,42 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>455</v>
+        <v>196</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12670,19 +12756,19 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>457</v>
+        <v>198</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>81</v>
@@ -12700,7 +12786,7 @@
         <v>81</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>81</v>
@@ -12711,21 +12797,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -12737,15 +12823,17 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>596</v>
+        <v>139</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12794,19 +12882,19 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>595</v>
+        <v>205</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -12824,7 +12912,7 @@
         <v>81</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>81</v>
@@ -12835,42 +12923,46 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>348</v>
+        <v>138</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>599</v>
+        <v>478</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -12918,19 +13010,19 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>598</v>
+        <v>480</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
@@ -12959,10 +13051,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12973,7 +13065,7 @@
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12985,13 +13077,13 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>171</v>
+        <v>330</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13018,13 +13110,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>604</v>
+        <v>81</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>605</v>
+        <v>81</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -13042,13 +13134,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -13069,10 +13161,10 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>81</v>
+        <v>599</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>135</v>
+        <v>325</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>81</v>
@@ -13083,10 +13175,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13094,13 +13186,13 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>81</v>
@@ -13109,17 +13201,15 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13156,20 +13246,22 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>92</v>
@@ -13181,7 +13273,7 @@
         <v>104</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>81</v>
+        <v>604</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>81</v>
@@ -13193,10 +13285,10 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>81</v>
+        <v>605</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>135</v>
+        <v>606</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>81</v>
@@ -13207,14 +13299,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>81</v>
       </c>
@@ -13226,7 +13316,7 @@
         <v>92</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>81</v>
@@ -13235,7 +13325,7 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>608</v>
@@ -13243,9 +13333,7 @@
       <c r="M88" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N88" t="s" s="2">
-        <v>610</v>
-      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -13294,10 +13382,10 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>92</v>
@@ -13309,22 +13397,22 @@
         <v>104</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>613</v>
+        <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>614</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>615</v>
+        <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>135</v>
+        <v>611</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>81</v>
@@ -13335,10 +13423,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13349,7 +13437,7 @@
         <v>82</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
@@ -13361,17 +13449,15 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>607</v>
+        <v>468</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13420,13 +13506,13 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>81</v>
@@ -13459,8 +13545,1136 @@
         <v>81</v>
       </c>
     </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR90" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR91" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR92" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR93" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR94" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR95" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AC96" s="2"/>
+      <c r="AD96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR96" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR97" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR98" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AR89">
+  <autoFilter ref="A1:AR98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13470,7 +14684,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -950,7 +950,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>333: reference based on V IMMUNIZATION - PATIENT NAME (9000010.11-.02)</t>
+    <t>333: reference based on V IMMUNIZATION - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.11-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Immun.Immunization.PatientIEN</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImmunizationImmunization.xlsx
+++ b/docs/StructureDefinition-ImmunizationImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
